--- a/code/ensemble_parameter_estimation/Python/Source_PowerDissipation_Temperature/Validation2.xlsx
+++ b/code/ensemble_parameter_estimation/Python/Source_PowerDissipation_Temperature/Validation2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trw1-my.sharepoint.com/personal/neel_padmanabhan_zf_com/Documents/Documents/EMB/AP/Thermal Analysis/ROM/Electronics_Motor_Disc/Rank 3 model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trw1-my.sharepoint.com/personal/neel_padmanabhan_zf_com/Documents/Documents/Paper/Github/Repository/Lumped-Parameter-Linear-Superposition-LPLSP/code/ensemble_parameter_estimation/Python/Source_PowerDissipation_Temperature/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="8_{366A8DC4-F71D-4209-BC64-C277DED7557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE5A0FAC-E361-4B10-BA29-51DBA5A4333E}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{366A8DC4-F71D-4209-BC64-C277DED7557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C27F697-62CF-4A0A-A8F9-146DB1FCD54A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{951BE81E-92E2-42DD-8981-6F50081DAFB9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{951BE81E-92E2-42DD-8981-6F50081DAFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerDissipation_11s" sheetId="3" r:id="rId1"/>
@@ -39,174 +39,6 @@
     <t>t</t>
   </si>
   <si>
-    <t>P_Q2000</t>
-  </si>
-  <si>
-    <t>P_Q2001</t>
-  </si>
-  <si>
-    <t>P_Q2002</t>
-  </si>
-  <si>
-    <t>P_Q2003</t>
-  </si>
-  <si>
-    <t>P_Q2004</t>
-  </si>
-  <si>
-    <t>P_Q2005</t>
-  </si>
-  <si>
-    <t>P_R2016</t>
-  </si>
-  <si>
-    <t>P_L2000</t>
-  </si>
-  <si>
-    <t>P_Q1500</t>
-  </si>
-  <si>
-    <t>P_Q1501</t>
-  </si>
-  <si>
-    <t>P_Q11504</t>
-  </si>
-  <si>
-    <t>P_Q11505</t>
-  </si>
-  <si>
-    <t>P_C2012</t>
-  </si>
-  <si>
-    <t>P_C2013</t>
-  </si>
-  <si>
-    <t>P_C2077</t>
-  </si>
-  <si>
-    <t>P_IC20000</t>
-  </si>
-  <si>
-    <t>P_IC9000</t>
-  </si>
-  <si>
-    <t>P_IC10601</t>
-  </si>
-  <si>
-    <t>P_IC31900</t>
-  </si>
-  <si>
-    <t>T_Q2000_Junction</t>
-  </si>
-  <si>
-    <t>T_Q2000_Case</t>
-  </si>
-  <si>
-    <t>T_Q2001_Junction</t>
-  </si>
-  <si>
-    <t>T_Q2001_Case</t>
-  </si>
-  <si>
-    <t>T_Q2002_Junction</t>
-  </si>
-  <si>
-    <t>T_Q2002_Case</t>
-  </si>
-  <si>
-    <t>T_Q2003_Junction</t>
-  </si>
-  <si>
-    <t>T_Q2003_Case</t>
-  </si>
-  <si>
-    <t>T_Q2004_Junction</t>
-  </si>
-  <si>
-    <t>T_Q2004_Case</t>
-  </si>
-  <si>
-    <t>T_Q2005_Junction</t>
-  </si>
-  <si>
-    <t>T_Q2005_Case</t>
-  </si>
-  <si>
-    <t>T_R2016</t>
-  </si>
-  <si>
-    <t>T_L2000_Source</t>
-  </si>
-  <si>
-    <t>T_L2000_Case</t>
-  </si>
-  <si>
-    <t>T_Q1500_Junction</t>
-  </si>
-  <si>
-    <t>T_Q1500_Case</t>
-  </si>
-  <si>
-    <t>T_Q1501_Junction</t>
-  </si>
-  <si>
-    <t>T_Q1501_Case</t>
-  </si>
-  <si>
-    <t>T_Q11504_Junction</t>
-  </si>
-  <si>
-    <t>T_Q11504_Case</t>
-  </si>
-  <si>
-    <t>T_Q11505_Junction</t>
-  </si>
-  <si>
-    <t>T_Q11505_Case</t>
-  </si>
-  <si>
-    <t>T_C2012_Src</t>
-  </si>
-  <si>
-    <t>T_C2012_Case</t>
-  </si>
-  <si>
-    <t>T_C2013_Src</t>
-  </si>
-  <si>
-    <t>T_C2013_Case</t>
-  </si>
-  <si>
-    <t>T_C2077_Src</t>
-  </si>
-  <si>
-    <t>T_C2077_Case</t>
-  </si>
-  <si>
-    <t>T_IC20000_Src</t>
-  </si>
-  <si>
-    <t>T_IC20000_Case</t>
-  </si>
-  <si>
-    <t>T_IC9000_Src</t>
-  </si>
-  <si>
-    <t>T_IC9000_Case</t>
-  </si>
-  <si>
-    <t>T_IC10601_Src</t>
-  </si>
-  <si>
-    <t>T_IC10601_Case</t>
-  </si>
-  <si>
-    <t>T_IC31900</t>
-  </si>
-  <si>
-    <t>T_PCBA</t>
-  </si>
-  <si>
     <t>T_S1</t>
   </si>
   <si>
@@ -218,12 +50,180 @@
   <si>
     <t>PREDICTIONS FROM ROM with Rank r=3</t>
   </si>
+  <si>
+    <t>T_1_Junction</t>
+  </si>
+  <si>
+    <t>T_1_Case</t>
+  </si>
+  <si>
+    <t>T_2_Junction</t>
+  </si>
+  <si>
+    <t>T_2_Case</t>
+  </si>
+  <si>
+    <t>T_3_Junction</t>
+  </si>
+  <si>
+    <t>T_3_Case</t>
+  </si>
+  <si>
+    <t>T_4_Junction</t>
+  </si>
+  <si>
+    <t>T_4_Case</t>
+  </si>
+  <si>
+    <t>T_5_Junction</t>
+  </si>
+  <si>
+    <t>T_5_Case</t>
+  </si>
+  <si>
+    <t>T_6_Junction</t>
+  </si>
+  <si>
+    <t>T_6_Case</t>
+  </si>
+  <si>
+    <t>T_7</t>
+  </si>
+  <si>
+    <t>T_8_Src</t>
+  </si>
+  <si>
+    <t>T_8_Case</t>
+  </si>
+  <si>
+    <t>T_9_Junction</t>
+  </si>
+  <si>
+    <t>T_9_Case</t>
+  </si>
+  <si>
+    <t>T_10_Junction</t>
+  </si>
+  <si>
+    <t>T_10_Case</t>
+  </si>
+  <si>
+    <t>T_11_Junction</t>
+  </si>
+  <si>
+    <t>T_11_Case</t>
+  </si>
+  <si>
+    <t>T_12_Junction</t>
+  </si>
+  <si>
+    <t>T_12_Case</t>
+  </si>
+  <si>
+    <t>T_13_Src</t>
+  </si>
+  <si>
+    <t>T_13_Case</t>
+  </si>
+  <si>
+    <t>T_14_Src</t>
+  </si>
+  <si>
+    <t>T_14_Case</t>
+  </si>
+  <si>
+    <t>T_15_Src</t>
+  </si>
+  <si>
+    <t>T_15_Case</t>
+  </si>
+  <si>
+    <t>T_16_Src</t>
+  </si>
+  <si>
+    <t>T_16_Case</t>
+  </si>
+  <si>
+    <t>T_17_Src</t>
+  </si>
+  <si>
+    <t>T_17_Case</t>
+  </si>
+  <si>
+    <t>T_18_Src</t>
+  </si>
+  <si>
+    <t>T_18_Case</t>
+  </si>
+  <si>
+    <t>T_19</t>
+  </si>
+  <si>
+    <t>T_PCB</t>
+  </si>
+  <si>
+    <t>P_1</t>
+  </si>
+  <si>
+    <t>P_2</t>
+  </si>
+  <si>
+    <t>P_3</t>
+  </si>
+  <si>
+    <t>P_4</t>
+  </si>
+  <si>
+    <t>P_5</t>
+  </si>
+  <si>
+    <t>P_6</t>
+  </si>
+  <si>
+    <t>P_7</t>
+  </si>
+  <si>
+    <t>P_8</t>
+  </si>
+  <si>
+    <t>P_9</t>
+  </si>
+  <si>
+    <t>P_10</t>
+  </si>
+  <si>
+    <t>P_11</t>
+  </si>
+  <si>
+    <t>P_12</t>
+  </si>
+  <si>
+    <t>P_13</t>
+  </si>
+  <si>
+    <t>P_14</t>
+  </si>
+  <si>
+    <t>P_15</t>
+  </si>
+  <si>
+    <t>P_16</t>
+  </si>
+  <si>
+    <t>P_17</t>
+  </si>
+  <si>
+    <t>P_18</t>
+  </si>
+  <si>
+    <t>P_19</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,12 +257,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -272,27 +266,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -310,7 +289,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -330,13 +309,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -352,10 +328,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -774,70 +746,70 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -3097,115 +3069,115 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.2">
@@ -6074,7 +6046,7 @@
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -6115,3714 +6087,3714 @@
       <c r="AL28" s="6"/>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="R29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="S29" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="T29" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="U29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="V29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="W29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="X29" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="Y29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="Z29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="AA29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M29" s="7" t="s">
+      <c r="AB29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="AC29" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O29" s="7" t="s">
+      <c r="AD29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P29" s="7" t="s">
+      <c r="AE29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q29" s="7" t="s">
+      <c r="AF29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="R29" s="7" t="s">
+      <c r="AG29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S29" s="7" t="s">
+      <c r="AH29" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="T29" s="7" t="s">
+      <c r="AI29" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U29" s="7" t="s">
+      <c r="AJ29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="V29" s="7" t="s">
+      <c r="AK29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="W29" s="7" t="s">
+      <c r="AL29" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="X29" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z29" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA29" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB29" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC29" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD29" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE29" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF29" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG29" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH29" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI29" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ29" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK29" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL29" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+      <c r="A30" s="7">
         <v>0</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="7">
         <v>20</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="7">
         <v>20</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="7">
         <v>20</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="7">
         <v>20</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="7">
         <v>20</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="7">
         <v>20</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="7">
         <v>20</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="7">
         <v>20</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="7">
         <v>20</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="7">
         <v>20</v>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="7">
         <v>20</v>
       </c>
-      <c r="M30" s="9">
+      <c r="M30" s="7">
         <v>20</v>
       </c>
-      <c r="N30" s="9">
+      <c r="N30" s="7">
         <v>20</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="7">
         <v>20</v>
       </c>
-      <c r="P30" s="9">
+      <c r="P30" s="7">
         <v>20</v>
       </c>
-      <c r="Q30" s="9">
+      <c r="Q30" s="7">
         <v>20</v>
       </c>
-      <c r="R30" s="9">
+      <c r="R30" s="7">
         <v>20</v>
       </c>
-      <c r="S30" s="9">
+      <c r="S30" s="7">
         <v>20</v>
       </c>
-      <c r="T30" s="9">
+      <c r="T30" s="7">
         <v>20</v>
       </c>
-      <c r="U30" s="9">
+      <c r="U30" s="7">
         <v>20</v>
       </c>
-      <c r="V30" s="9">
+      <c r="V30" s="7">
         <v>20</v>
       </c>
-      <c r="W30" s="9">
+      <c r="W30" s="7">
         <v>20</v>
       </c>
-      <c r="X30" s="9">
+      <c r="X30" s="7">
         <v>20</v>
       </c>
-      <c r="Y30" s="9">
+      <c r="Y30" s="7">
         <v>20</v>
       </c>
-      <c r="Z30" s="9">
+      <c r="Z30" s="7">
         <v>20</v>
       </c>
-      <c r="AA30" s="9">
+      <c r="AA30" s="7">
         <v>20</v>
       </c>
-      <c r="AB30" s="9">
+      <c r="AB30" s="7">
         <v>20</v>
       </c>
-      <c r="AC30" s="9">
+      <c r="AC30" s="7">
         <v>20</v>
       </c>
-      <c r="AD30" s="9">
+      <c r="AD30" s="7">
         <v>20</v>
       </c>
-      <c r="AE30" s="9">
+      <c r="AE30" s="7">
         <v>20</v>
       </c>
-      <c r="AF30" s="9">
+      <c r="AF30" s="7">
         <v>20</v>
       </c>
-      <c r="AG30" s="9">
+      <c r="AG30" s="7">
         <v>20</v>
       </c>
-      <c r="AH30" s="9">
+      <c r="AH30" s="7">
         <v>20</v>
       </c>
-      <c r="AI30" s="9">
+      <c r="AI30" s="7">
         <v>20</v>
       </c>
-      <c r="AJ30" s="9">
+      <c r="AJ30" s="7">
         <v>20</v>
       </c>
-      <c r="AK30" s="9">
+      <c r="AK30" s="7">
         <v>20</v>
       </c>
-      <c r="AL30" s="9">
+      <c r="AL30" s="7">
         <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+      <c r="A31" s="7">
         <v>0.5</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="7">
         <v>20.525304194365969</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="7">
         <v>20.46261787895568</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="7">
         <v>21.407523868695201</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="7">
         <v>21.237349147474639</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="7">
         <v>23.970906603814321</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="7">
         <v>23.49429842294278</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="7">
         <v>20.98217988786714</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="7">
         <v>20.840622701454219</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="7">
         <v>20.3062039382487</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="7">
         <v>20.263345458345341</v>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="7">
         <v>21.424485650597681</v>
       </c>
-      <c r="M31" s="9">
+      <c r="M31" s="7">
         <v>21.251895744110879</v>
       </c>
-      <c r="N31" s="9">
+      <c r="N31" s="7">
         <v>27.978769950497028</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O31" s="7">
         <v>20.14431233675937</v>
       </c>
-      <c r="P31" s="9">
+      <c r="P31" s="7">
         <v>20.68190879962054</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="Q31" s="7">
         <v>20.61782822742569</v>
       </c>
-      <c r="R31" s="9">
+      <c r="R31" s="7">
         <v>20.477832509569151</v>
       </c>
-      <c r="S31" s="9">
+      <c r="S31" s="7">
         <v>21.408196565480139</v>
       </c>
-      <c r="T31" s="9">
+      <c r="T31" s="7">
         <v>21.31522252344163</v>
       </c>
-      <c r="U31" s="9">
+      <c r="U31" s="7">
         <v>20.999626005127979</v>
       </c>
-      <c r="V31" s="9">
+      <c r="V31" s="7">
         <v>20.850652646873741</v>
       </c>
-      <c r="W31" s="9">
+      <c r="W31" s="7">
         <v>20.612726052052519</v>
       </c>
-      <c r="X31" s="9">
+      <c r="X31" s="7">
         <v>20.493403176284751</v>
       </c>
-      <c r="Y31" s="9">
+      <c r="Y31" s="7">
         <v>20.099172154110299</v>
       </c>
-      <c r="Z31" s="9">
+      <c r="Z31" s="7">
         <v>20.073100577599309</v>
       </c>
-      <c r="AA31" s="9">
+      <c r="AA31" s="7">
         <v>20.050276049234071</v>
       </c>
-      <c r="AB31" s="9">
+      <c r="AB31" s="7">
         <v>20.047122676306479</v>
       </c>
-      <c r="AC31" s="9">
+      <c r="AC31" s="7">
         <v>20.10350284373796</v>
       </c>
-      <c r="AD31" s="9">
+      <c r="AD31" s="7">
         <v>20.085902216893111</v>
       </c>
-      <c r="AE31" s="9">
+      <c r="AE31" s="7">
         <v>20.216906404886849</v>
       </c>
-      <c r="AF31" s="9">
+      <c r="AF31" s="7">
         <v>20.719580510013209</v>
       </c>
-      <c r="AG31" s="9">
+      <c r="AG31" s="7">
         <v>20.249284648949139</v>
       </c>
-      <c r="AH31" s="9">
+      <c r="AH31" s="7">
         <v>20.237972937430779</v>
       </c>
-      <c r="AI31" s="9">
+      <c r="AI31" s="7">
         <v>20.98869343933913</v>
       </c>
-      <c r="AJ31" s="9">
+      <c r="AJ31" s="7">
         <v>20.987280334256731</v>
       </c>
-      <c r="AK31" s="9">
+      <c r="AK31" s="7">
         <v>22.448752564646551</v>
       </c>
-      <c r="AL31" s="9">
+      <c r="AL31" s="7">
         <v>22.279680318170541</v>
       </c>
     </row>
     <row r="32" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
+      <c r="A32" s="7">
         <v>1</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="7">
         <v>21.70017168262039</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="7">
         <v>21.570663030300611</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="7">
         <v>21.47164802209786</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="7">
         <v>21.422064430697059</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="7">
         <v>22.45160465346202</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="7">
         <v>22.5178484493123</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="7">
         <v>25.771457508644581</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="7">
         <v>25.073767548708538</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="7">
         <v>21.028572262763539</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="7">
         <v>20.953093748136709</v>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="7">
         <v>22.254733386704721</v>
       </c>
-      <c r="M32" s="9">
+      <c r="M32" s="7">
         <v>22.114319173093929</v>
       </c>
-      <c r="N32" s="9">
+      <c r="N32" s="7">
         <v>27.777956810829181</v>
       </c>
-      <c r="O32" s="9">
+      <c r="O32" s="7">
         <v>20.399388065614499</v>
       </c>
-      <c r="P32" s="9">
+      <c r="P32" s="7">
         <v>21.909173217554059</v>
       </c>
-      <c r="Q32" s="9">
+      <c r="Q32" s="7">
         <v>21.723081406745472</v>
       </c>
-      <c r="R32" s="9">
+      <c r="R32" s="7">
         <v>21.338678844417348</v>
       </c>
-      <c r="S32" s="9">
+      <c r="S32" s="7">
         <v>22.554115243985201</v>
       </c>
-      <c r="T32" s="9">
+      <c r="T32" s="7">
         <v>22.408961735714978</v>
       </c>
-      <c r="U32" s="9">
+      <c r="U32" s="7">
         <v>21.255933639721359</v>
       </c>
-      <c r="V32" s="9">
+      <c r="V32" s="7">
         <v>21.08052555527021</v>
       </c>
-      <c r="W32" s="9">
+      <c r="W32" s="7">
         <v>21.634296707013451</v>
       </c>
-      <c r="X32" s="9">
+      <c r="X32" s="7">
         <v>21.315217391129231</v>
       </c>
-      <c r="Y32" s="9">
+      <c r="Y32" s="7">
         <v>20.18638957128729</v>
       </c>
-      <c r="Z32" s="9">
+      <c r="Z32" s="7">
         <v>20.15555217614337</v>
       </c>
-      <c r="AA32" s="9">
+      <c r="AA32" s="7">
         <v>20.125570292715821</v>
       </c>
-      <c r="AB32" s="9">
+      <c r="AB32" s="7">
         <v>20.117399230122441</v>
       </c>
-      <c r="AC32" s="9">
+      <c r="AC32" s="7">
         <v>20.19633178836386</v>
       </c>
-      <c r="AD32" s="9">
+      <c r="AD32" s="7">
         <v>20.17297617860882</v>
       </c>
-      <c r="AE32" s="9">
+      <c r="AE32" s="7">
         <v>20.577463406792479</v>
       </c>
-      <c r="AF32" s="9">
+      <c r="AF32" s="7">
         <v>22.323721827289312</v>
       </c>
-      <c r="AG32" s="9">
+      <c r="AG32" s="7">
         <v>20.491225525625719</v>
       </c>
-      <c r="AH32" s="9">
+      <c r="AH32" s="7">
         <v>20.480623188582079</v>
       </c>
-      <c r="AI32" s="9">
+      <c r="AI32" s="7">
         <v>21.69600310463489</v>
       </c>
-      <c r="AJ32" s="9">
+      <c r="AJ32" s="7">
         <v>21.71218315468715</v>
       </c>
-      <c r="AK32" s="9">
+      <c r="AK32" s="7">
         <v>23.49077853338958</v>
       </c>
-      <c r="AL32" s="9">
+      <c r="AL32" s="7">
         <v>22.077274369393489</v>
       </c>
     </row>
     <row r="33" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+      <c r="A33" s="7">
         <v>1.5</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="7">
         <v>21.755184192811321</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="7">
         <v>21.77162309196229</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="7">
         <v>22.299088783182491</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="7">
         <v>22.235388764022002</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="7">
         <v>26.311466145586579</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="7">
         <v>25.812902446024921</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="7">
         <v>27.233674959347159</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="7">
         <v>26.812217107717291</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="7">
         <v>21.801545038135739</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="7">
         <v>21.724609906426771</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="7">
         <v>23.05830564061699</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="7">
         <v>22.953855228596641</v>
       </c>
-      <c r="N33" s="9">
+      <c r="N33" s="7">
         <v>26.301661130038301</v>
       </c>
-      <c r="O33" s="9">
+      <c r="O33" s="7">
         <v>20.78457667837398</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P33" s="7">
         <v>23.72098276138702</v>
       </c>
-      <c r="Q33" s="9">
+      <c r="Q33" s="7">
         <v>21.704574296935011</v>
       </c>
-      <c r="R33" s="9">
+      <c r="R33" s="7">
         <v>21.554272248837911</v>
       </c>
-      <c r="S33" s="9">
+      <c r="S33" s="7">
         <v>23.39609046571864</v>
       </c>
-      <c r="T33" s="9">
+      <c r="T33" s="7">
         <v>22.71399195573516</v>
       </c>
-      <c r="U33" s="9">
+      <c r="U33" s="7">
         <v>21.68592512430893</v>
       </c>
-      <c r="V33" s="9">
+      <c r="V33" s="7">
         <v>21.415256587394438</v>
       </c>
-      <c r="W33" s="9">
+      <c r="W33" s="7">
         <v>21.802595450946932</v>
       </c>
-      <c r="X33" s="9">
+      <c r="X33" s="7">
         <v>21.620138193902921</v>
       </c>
-      <c r="Y33" s="9">
+      <c r="Y33" s="7">
         <v>20.302740221612769</v>
       </c>
-      <c r="Z33" s="9">
+      <c r="Z33" s="7">
         <v>20.27052249120597</v>
       </c>
-      <c r="AA33" s="9">
+      <c r="AA33" s="7">
         <v>20.215982050477809</v>
       </c>
-      <c r="AB33" s="9">
+      <c r="AB33" s="7">
         <v>20.206236534817439</v>
       </c>
-      <c r="AC33" s="9">
+      <c r="AC33" s="7">
         <v>20.336118523641652</v>
       </c>
-      <c r="AD33" s="9">
+      <c r="AD33" s="7">
         <v>20.312362396294141</v>
       </c>
-      <c r="AE33" s="9">
+      <c r="AE33" s="7">
         <v>20.983068637006589</v>
       </c>
-      <c r="AF33" s="9">
+      <c r="AF33" s="7">
         <v>23.76995608373565</v>
       </c>
-      <c r="AG33" s="9">
+      <c r="AG33" s="7">
         <v>27.844300911920371</v>
       </c>
-      <c r="AH33" s="9">
+      <c r="AH33" s="7">
         <v>27.212645510829041</v>
       </c>
-      <c r="AI33" s="9">
+      <c r="AI33" s="7">
         <v>22.554181735160491</v>
       </c>
-      <c r="AJ33" s="9">
+      <c r="AJ33" s="7">
         <v>22.608028557537569</v>
       </c>
-      <c r="AK33" s="9">
+      <c r="AK33" s="7">
         <v>24.355524364017171</v>
       </c>
-      <c r="AL33" s="9">
+      <c r="AL33" s="7">
         <v>24.4076488063574</v>
       </c>
     </row>
     <row r="34" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
+      <c r="A34" s="7">
         <v>2</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="7">
         <v>22.297341307691699</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="7">
         <v>22.273769644169811</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="7">
         <v>22.353931878224209</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="7">
         <v>22.33645345958579</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="7">
         <v>25.390595364344168</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="7">
         <v>25.374872194361291</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="7">
         <v>26.98394588021872</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="7">
         <v>26.852350487013691</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="7">
         <v>22.396415414485499</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="7">
         <v>22.305665590587509</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="7">
         <v>22.77480350136786</v>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="7">
         <v>22.807857763277411</v>
       </c>
-      <c r="N34" s="9">
+      <c r="N34" s="7">
         <v>27.081325800995781</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="7">
         <v>21.047603528117691</v>
       </c>
-      <c r="P34" s="9">
+      <c r="P34" s="7">
         <v>24.608591831519671</v>
       </c>
-      <c r="Q34" s="9">
+      <c r="Q34" s="7">
         <v>22.38953215554675</v>
       </c>
-      <c r="R34" s="9">
+      <c r="R34" s="7">
         <v>22.087031143506401</v>
       </c>
-      <c r="S34" s="9">
+      <c r="S34" s="7">
         <v>23.416715603771269</v>
       </c>
-      <c r="T34" s="9">
+      <c r="T34" s="7">
         <v>23.22795224555345</v>
       </c>
-      <c r="U34" s="9">
+      <c r="U34" s="7">
         <v>21.84516158485437</v>
       </c>
-      <c r="V34" s="9">
+      <c r="V34" s="7">
         <v>21.665402165795449</v>
       </c>
-      <c r="W34" s="9">
+      <c r="W34" s="7">
         <v>22.186007799412</v>
       </c>
-      <c r="X34" s="9">
+      <c r="X34" s="7">
         <v>21.97280497491041</v>
       </c>
-      <c r="Y34" s="9">
+      <c r="Y34" s="7">
         <v>20.356643922958629</v>
       </c>
-      <c r="Z34" s="9">
+      <c r="Z34" s="7">
         <v>20.318337715850969</v>
       </c>
-      <c r="AA34" s="9">
+      <c r="AA34" s="7">
         <v>20.24552628732868</v>
       </c>
-      <c r="AB34" s="9">
+      <c r="AB34" s="7">
         <v>20.235434921624641</v>
       </c>
-      <c r="AC34" s="9">
+      <c r="AC34" s="7">
         <v>20.41798318064528</v>
       </c>
-      <c r="AD34" s="9">
+      <c r="AD34" s="7">
         <v>20.39062592683138</v>
       </c>
-      <c r="AE34" s="9">
+      <c r="AE34" s="7">
         <v>21.225318477052291</v>
       </c>
-      <c r="AF34" s="9">
+      <c r="AF34" s="7">
         <v>24.750594689820741</v>
       </c>
-      <c r="AG34" s="9">
+      <c r="AG34" s="7">
         <v>24.668857824542361</v>
       </c>
-      <c r="AH34" s="9">
+      <c r="AH34" s="7">
         <v>24.327331206022411</v>
       </c>
-      <c r="AI34" s="9">
+      <c r="AI34" s="7">
         <v>22.708673291168559</v>
       </c>
-      <c r="AJ34" s="9">
+      <c r="AJ34" s="7">
         <v>22.76319835435504</v>
       </c>
-      <c r="AK34" s="9">
+      <c r="AK34" s="7">
         <v>25.061414118812738</v>
       </c>
-      <c r="AL34" s="9">
+      <c r="AL34" s="7">
         <v>24.513727977663251</v>
       </c>
     </row>
     <row r="35" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
+      <c r="A35" s="7">
         <v>2.5</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="7">
         <v>23.280506692674511</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="7">
         <v>23.166109704468681</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="7">
         <v>22.946265000696719</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="7">
         <v>22.873886245221211</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="7">
         <v>23.923837186002469</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="7">
         <v>24.079149238565861</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="7">
         <v>26.807380483335461</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="7">
         <v>26.752327988301001</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="7">
         <v>22.931912823595201</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="7">
         <v>22.851173829043379</v>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="7">
         <v>23.255597939607139</v>
       </c>
-      <c r="M35" s="9">
+      <c r="M35" s="7">
         <v>23.204415739599021</v>
       </c>
-      <c r="N35" s="9">
+      <c r="N35" s="7">
         <v>25.52207846423082</v>
       </c>
-      <c r="O35" s="9">
+      <c r="O35" s="7">
         <v>21.338581350132671</v>
       </c>
-      <c r="P35" s="9">
+      <c r="P35" s="7">
         <v>25.85826188123194</v>
       </c>
-      <c r="Q35" s="9">
+      <c r="Q35" s="7">
         <v>22.172378398628439</v>
       </c>
-      <c r="R35" s="9">
+      <c r="R35" s="7">
         <v>22.138698032250652</v>
       </c>
-      <c r="S35" s="9">
+      <c r="S35" s="7">
         <v>23.64734282620455</v>
       </c>
-      <c r="T35" s="9">
+      <c r="T35" s="7">
         <v>23.01074609217866</v>
       </c>
-      <c r="U35" s="9">
+      <c r="U35" s="7">
         <v>22.0795231010596</v>
       </c>
-      <c r="V35" s="9">
+      <c r="V35" s="7">
         <v>21.862996252095979</v>
       </c>
-      <c r="W35" s="9">
+      <c r="W35" s="7">
         <v>22.39990637779545</v>
       </c>
-      <c r="X35" s="9">
+      <c r="X35" s="7">
         <v>22.232195398505691</v>
       </c>
-      <c r="Y35" s="9">
+      <c r="Y35" s="7">
         <v>20.462942106466262</v>
       </c>
-      <c r="Z35" s="9">
+      <c r="Z35" s="7">
         <v>20.421106970696592</v>
       </c>
-      <c r="AA35" s="9">
+      <c r="AA35" s="7">
         <v>20.33870584693371</v>
       </c>
-      <c r="AB35" s="9">
+      <c r="AB35" s="7">
         <v>20.3261392841389</v>
       </c>
-      <c r="AC35" s="9">
+      <c r="AC35" s="7">
         <v>20.524904427319779</v>
       </c>
-      <c r="AD35" s="9">
+      <c r="AD35" s="7">
         <v>20.496873059954599</v>
       </c>
-      <c r="AE35" s="9">
+      <c r="AE35" s="7">
         <v>21.449324635841769</v>
       </c>
-      <c r="AF35" s="9">
+      <c r="AF35" s="7">
         <v>25.43775703815616</v>
       </c>
-      <c r="AG35" s="9">
+      <c r="AG35" s="7">
         <v>28.78973025892472</v>
       </c>
-      <c r="AH35" s="9">
+      <c r="AH35" s="7">
         <v>28.11399008098876</v>
       </c>
-      <c r="AI35" s="9">
+      <c r="AI35" s="7">
         <v>22.856816934502049</v>
       </c>
-      <c r="AJ35" s="9">
+      <c r="AJ35" s="7">
         <v>22.904688317312651</v>
       </c>
-      <c r="AK35" s="9">
+      <c r="AK35" s="7">
         <v>25.369183777728072</v>
       </c>
-      <c r="AL35" s="9">
+      <c r="AL35" s="7">
         <v>23.83376365922901</v>
       </c>
     </row>
     <row r="36" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
+      <c r="A36" s="7">
         <v>3</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="7">
         <v>23.43173043267802</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="7">
         <v>23.398134350560461</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="7">
         <v>23.22946655403663</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="7">
         <v>23.185330892164071</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="7">
         <v>25.90761680345048</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="7">
         <v>25.668542925669641</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="7">
         <v>27.223702631303201</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="7">
         <v>27.122897576692491</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="7">
         <v>23.51422528234967</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="7">
         <v>23.419413340435469</v>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="7">
         <v>23.21619132155211</v>
       </c>
-      <c r="M36" s="9">
+      <c r="M36" s="7">
         <v>23.214629426501499</v>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="7">
         <v>27.820643467426699</v>
       </c>
-      <c r="O36" s="9">
+      <c r="O36" s="7">
         <v>21.608630311127211</v>
       </c>
-      <c r="P36" s="9">
+      <c r="P36" s="7">
         <v>26.423122007806061</v>
       </c>
-      <c r="Q36" s="9">
+      <c r="Q36" s="7">
         <v>22.996698402328668</v>
       </c>
-      <c r="R36" s="9">
+      <c r="R36" s="7">
         <v>22.754959356720718</v>
       </c>
-      <c r="S36" s="9">
+      <c r="S36" s="7">
         <v>23.419083760711121</v>
       </c>
-      <c r="T36" s="9">
+      <c r="T36" s="7">
         <v>23.225340202988619</v>
       </c>
-      <c r="U36" s="9">
+      <c r="U36" s="7">
         <v>22.071859584481309</v>
       </c>
-      <c r="V36" s="9">
+      <c r="V36" s="7">
         <v>22.021476941536768</v>
       </c>
-      <c r="W36" s="9">
+      <c r="W36" s="7">
         <v>23.006299289922261</v>
       </c>
-      <c r="X36" s="9">
+      <c r="X36" s="7">
         <v>22.815673314836431</v>
       </c>
-      <c r="Y36" s="9">
+      <c r="Y36" s="7">
         <v>20.50770297928068</v>
       </c>
-      <c r="Z36" s="9">
+      <c r="Z36" s="7">
         <v>20.46726730495191</v>
       </c>
-      <c r="AA36" s="9">
+      <c r="AA36" s="7">
         <v>20.36561428350532</v>
       </c>
-      <c r="AB36" s="9">
+      <c r="AB36" s="7">
         <v>20.353328048719419</v>
       </c>
-      <c r="AC36" s="9">
+      <c r="AC36" s="7">
         <v>20.606795127256081</v>
       </c>
-      <c r="AD36" s="9">
+      <c r="AD36" s="7">
         <v>20.57852296961444</v>
       </c>
-      <c r="AE36" s="9">
+      <c r="AE36" s="7">
         <v>21.642215070522191</v>
       </c>
-      <c r="AF36" s="9">
+      <c r="AF36" s="7">
         <v>26.02683955403338</v>
       </c>
-      <c r="AG36" s="9">
+      <c r="AG36" s="7">
         <v>25.19242362996766</v>
       </c>
-      <c r="AH36" s="9">
+      <c r="AH36" s="7">
         <v>24.831333432374478</v>
       </c>
-      <c r="AI36" s="9">
+      <c r="AI36" s="7">
         <v>22.936895803538381</v>
       </c>
-      <c r="AJ36" s="9">
+      <c r="AJ36" s="7">
         <v>23.00484169536135</v>
       </c>
-      <c r="AK36" s="9">
+      <c r="AK36" s="7">
         <v>25.86593802039858</v>
       </c>
-      <c r="AL36" s="9">
+      <c r="AL36" s="7">
         <v>24.67398897881931</v>
       </c>
     </row>
     <row r="37" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
+      <c r="A37" s="7">
         <v>3.5</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="7">
         <v>24.457127501434272</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="7">
         <v>24.3339093292591</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="7">
         <v>24.50316617133555</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="7">
         <v>24.356632858958701</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="7">
         <v>26.100393698307169</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="7">
         <v>25.990241594942759</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="7">
         <v>24.478068613894202</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="7">
         <v>24.766726635640701</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="7">
         <v>23.96380621326745</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="7">
         <v>23.875009792207369</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="7">
         <v>23.72816265522167</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="7">
         <v>23.661294344095001</v>
       </c>
-      <c r="N37" s="9">
+      <c r="N37" s="7">
         <v>31.456441520882699</v>
       </c>
-      <c r="O37" s="9">
+      <c r="O37" s="7">
         <v>21.980282007268301</v>
       </c>
-      <c r="P37" s="9">
+      <c r="P37" s="7">
         <v>27.683132570228171</v>
       </c>
-      <c r="Q37" s="9">
+      <c r="Q37" s="7">
         <v>23.40309474966195</v>
       </c>
-      <c r="R37" s="9">
+      <c r="R37" s="7">
         <v>23.088914669914459</v>
       </c>
-      <c r="S37" s="9">
+      <c r="S37" s="7">
         <v>23.11701952070025</v>
       </c>
-      <c r="T37" s="9">
+      <c r="T37" s="7">
         <v>22.957155244653919</v>
       </c>
-      <c r="U37" s="9">
+      <c r="U37" s="7">
         <v>22.278285447937598</v>
       </c>
-      <c r="V37" s="9">
+      <c r="V37" s="7">
         <v>22.30497196171947</v>
       </c>
-      <c r="W37" s="9">
+      <c r="W37" s="7">
         <v>23.259078963224741</v>
       </c>
-      <c r="X37" s="9">
+      <c r="X37" s="7">
         <v>23.061846341644181</v>
       </c>
-      <c r="Y37" s="9">
+      <c r="Y37" s="7">
         <v>20.668784750415409</v>
       </c>
-      <c r="Z37" s="9">
+      <c r="Z37" s="7">
         <v>20.636708606758621</v>
       </c>
-      <c r="AA37" s="9">
+      <c r="AA37" s="7">
         <v>20.524953500184608</v>
       </c>
-      <c r="AB37" s="9">
+      <c r="AB37" s="7">
         <v>20.511589649097381</v>
       </c>
-      <c r="AC37" s="9">
+      <c r="AC37" s="7">
         <v>20.776254251525391</v>
       </c>
-      <c r="AD37" s="9">
+      <c r="AD37" s="7">
         <v>20.752949053391209</v>
       </c>
-      <c r="AE37" s="9">
+      <c r="AE37" s="7">
         <v>21.90505782322554</v>
       </c>
-      <c r="AF37" s="9">
+      <c r="AF37" s="7">
         <v>26.154910692010699</v>
       </c>
-      <c r="AG37" s="9">
+      <c r="AG37" s="7">
         <v>39.069039960639067</v>
       </c>
-      <c r="AH37" s="9">
+      <c r="AH37" s="7">
         <v>37.553718325456913</v>
       </c>
-      <c r="AI37" s="9">
+      <c r="AI37" s="7">
         <v>22.63792296877569</v>
       </c>
-      <c r="AJ37" s="9">
+      <c r="AJ37" s="7">
         <v>22.682362390722918</v>
       </c>
-      <c r="AK37" s="9">
+      <c r="AK37" s="7">
         <v>26.153561822384511</v>
       </c>
-      <c r="AL37" s="9">
+      <c r="AL37" s="7">
         <v>25.04976854728617</v>
       </c>
     </row>
     <row r="38" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
+      <c r="A38" s="7">
         <v>4</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="7">
         <v>24.82675924144722</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="7">
         <v>24.7615787935007</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="7">
         <v>24.059487168828142</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="7">
         <v>24.067222542999861</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="7">
         <v>27.161001634493449</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="7">
         <v>26.958780152938768</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="7">
         <v>26.9134376459225</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="7">
         <v>26.652140251771861</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="7">
         <v>24.472812535605382</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="7">
         <v>24.396846388953328</v>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="7">
         <v>24.805378062771851</v>
       </c>
-      <c r="M38" s="9">
+      <c r="M38" s="7">
         <v>24.667265819178802</v>
       </c>
-      <c r="N38" s="9">
+      <c r="N38" s="7">
         <v>26.829324822491721</v>
       </c>
-      <c r="O38" s="9">
+      <c r="O38" s="7">
         <v>22.31545963633873</v>
       </c>
-      <c r="P38" s="9">
+      <c r="P38" s="7">
         <v>29.0382005718639</v>
       </c>
-      <c r="Q38" s="9">
+      <c r="Q38" s="7">
         <v>24.068898020894469</v>
       </c>
-      <c r="R38" s="9">
+      <c r="R38" s="7">
         <v>23.747328399290119</v>
       </c>
-      <c r="S38" s="9">
+      <c r="S38" s="7">
         <v>24.342594722929359</v>
       </c>
-      <c r="T38" s="9">
+      <c r="T38" s="7">
         <v>23.055189651157519</v>
       </c>
-      <c r="U38" s="9">
+      <c r="U38" s="7">
         <v>23.049470344445009</v>
       </c>
-      <c r="V38" s="9">
+      <c r="V38" s="7">
         <v>22.67550584153409</v>
       </c>
-      <c r="W38" s="9">
+      <c r="W38" s="7">
         <v>24.152083888187839</v>
       </c>
-      <c r="X38" s="9">
+      <c r="X38" s="7">
         <v>23.81797001711654</v>
       </c>
-      <c r="Y38" s="9">
+      <c r="Y38" s="7">
         <v>20.818562537300121</v>
       </c>
-      <c r="Z38" s="9">
+      <c r="Z38" s="7">
         <v>20.776027131339831</v>
       </c>
-      <c r="AA38" s="9">
+      <c r="AA38" s="7">
         <v>20.639300694952372</v>
       </c>
-      <c r="AB38" s="9">
+      <c r="AB38" s="7">
         <v>20.62347394535027</v>
       </c>
-      <c r="AC38" s="9">
+      <c r="AC38" s="7">
         <v>20.923154768584649</v>
       </c>
-      <c r="AD38" s="9">
+      <c r="AD38" s="7">
         <v>20.896488499072959</v>
       </c>
-      <c r="AE38" s="9">
+      <c r="AE38" s="7">
         <v>22.11638922919408</v>
       </c>
-      <c r="AF38" s="9">
+      <c r="AF38" s="7">
         <v>26.533341059440161</v>
       </c>
-      <c r="AG38" s="9">
+      <c r="AG38" s="7">
         <v>35.90167229828873</v>
       </c>
-      <c r="AH38" s="9">
+      <c r="AH38" s="7">
         <v>34.702429339425372</v>
       </c>
-      <c r="AI38" s="9">
+      <c r="AI38" s="7">
         <v>23.314311583470761</v>
       </c>
-      <c r="AJ38" s="9">
+      <c r="AJ38" s="7">
         <v>23.361027041382989</v>
       </c>
-      <c r="AK38" s="9">
+      <c r="AK38" s="7">
         <v>26.64865400114271</v>
       </c>
-      <c r="AL38" s="9">
+      <c r="AL38" s="7">
         <v>25.985643449533381</v>
       </c>
     </row>
     <row r="39" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
+      <c r="A39" s="7">
         <v>4.5</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="7">
         <v>24.76979811073867</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="7">
         <v>24.773309701480379</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="7">
         <v>25.17127842204162</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="7">
         <v>25.03691574115026</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="7">
         <v>25.16273909534144</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="7">
         <v>25.375285031789829</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="7">
         <v>25.394832356372849</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="7">
         <v>25.487850281924828</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="7">
         <v>24.849341367266991</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="7">
         <v>24.778424896175359</v>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="7">
         <v>24.56515674116298</v>
       </c>
-      <c r="M39" s="9">
+      <c r="M39" s="7">
         <v>24.56213047496032</v>
       </c>
-      <c r="N39" s="9">
+      <c r="N39" s="7">
         <v>29.24562179544419</v>
       </c>
-      <c r="O39" s="9">
+      <c r="O39" s="7">
         <v>22.619456557958241</v>
       </c>
-      <c r="P39" s="9">
+      <c r="P39" s="7">
         <v>29.953706289461369</v>
       </c>
-      <c r="Q39" s="9">
+      <c r="Q39" s="7">
         <v>23.480096853981269</v>
       </c>
-      <c r="R39" s="9">
+      <c r="R39" s="7">
         <v>23.479027309406799</v>
       </c>
-      <c r="S39" s="9">
+      <c r="S39" s="7">
         <v>24.254576634409851</v>
       </c>
-      <c r="T39" s="9">
+      <c r="T39" s="7">
         <v>23.73748126984108</v>
       </c>
-      <c r="U39" s="9">
+      <c r="U39" s="7">
         <v>23.166687180114959</v>
       </c>
-      <c r="V39" s="9">
+      <c r="V39" s="7">
         <v>22.935698556565089</v>
       </c>
-      <c r="W39" s="9">
+      <c r="W39" s="7">
         <v>23.987445958917551</v>
       </c>
-      <c r="X39" s="9">
+      <c r="X39" s="7">
         <v>23.881539047186269</v>
       </c>
-      <c r="Y39" s="9">
+      <c r="Y39" s="7">
         <v>20.928858776542569</v>
       </c>
-      <c r="Z39" s="9">
+      <c r="Z39" s="7">
         <v>20.88286976476806</v>
       </c>
-      <c r="AA39" s="9">
+      <c r="AA39" s="7">
         <v>20.734562567804598</v>
       </c>
-      <c r="AB39" s="9">
+      <c r="AB39" s="7">
         <v>20.719174197057701</v>
       </c>
-      <c r="AC39" s="9">
+      <c r="AC39" s="7">
         <v>21.043965537513191</v>
       </c>
-      <c r="AD39" s="9">
+      <c r="AD39" s="7">
         <v>21.018390919469951</v>
       </c>
-      <c r="AE39" s="9">
+      <c r="AE39" s="7">
         <v>22.317259852770309</v>
       </c>
-      <c r="AF39" s="9">
+      <c r="AF39" s="7">
         <v>26.881192910259902</v>
       </c>
-      <c r="AG39" s="9">
+      <c r="AG39" s="7">
         <v>38.024002632465333</v>
       </c>
-      <c r="AH39" s="9">
+      <c r="AH39" s="7">
         <v>36.654853134301348</v>
       </c>
-      <c r="AI39" s="9">
+      <c r="AI39" s="7">
         <v>23.11682009186595</v>
       </c>
-      <c r="AJ39" s="9">
+      <c r="AJ39" s="7">
         <v>23.14204084172345</v>
       </c>
-      <c r="AK39" s="9">
+      <c r="AK39" s="7">
         <v>27.136497117225531</v>
       </c>
-      <c r="AL39" s="9">
+      <c r="AL39" s="7">
         <v>25.10170933014652</v>
       </c>
     </row>
     <row r="40" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A40" s="9">
+      <c r="A40" s="7">
         <v>5</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="7">
         <v>26.1691121153418</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="7">
         <v>26.031342190169649</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="7">
         <v>24.84259377562023</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="7">
         <v>24.86156363163062</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="7">
         <v>24.946904998028501</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="7">
         <v>25.004530157794239</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="7">
         <v>27.803937754373941</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="7">
         <v>27.46180752127454</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="7">
         <v>25.457854002970031</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="7">
         <v>25.41167893741882</v>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="7">
         <v>24.854120168228569</v>
       </c>
-      <c r="M40" s="9">
+      <c r="M40" s="7">
         <v>24.80533683601125</v>
       </c>
-      <c r="N40" s="9">
+      <c r="N40" s="7">
         <v>27.489913186847659</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="7">
         <v>23.05716504739576</v>
       </c>
-      <c r="P40" s="9">
+      <c r="P40" s="7">
         <v>31.795044651876129</v>
       </c>
-      <c r="Q40" s="9">
+      <c r="Q40" s="7">
         <v>23.842751675448401</v>
       </c>
-      <c r="R40" s="9">
+      <c r="R40" s="7">
         <v>23.73534890056078</v>
       </c>
-      <c r="S40" s="9">
+      <c r="S40" s="7">
         <v>24.888673228753831</v>
       </c>
-      <c r="T40" s="9">
+      <c r="T40" s="7">
         <v>24.58895821597627</v>
       </c>
-      <c r="U40" s="9">
+      <c r="U40" s="7">
         <v>23.325835542726011</v>
       </c>
-      <c r="V40" s="9">
+      <c r="V40" s="7">
         <v>23.057103384268789</v>
       </c>
-      <c r="W40" s="9">
+      <c r="W40" s="7">
         <v>23.886025209833399</v>
       </c>
-      <c r="X40" s="9">
+      <c r="X40" s="7">
         <v>23.848959617196769</v>
       </c>
-      <c r="Y40" s="9">
+      <c r="Y40" s="7">
         <v>21.09686738833387</v>
       </c>
-      <c r="Z40" s="9">
+      <c r="Z40" s="7">
         <v>21.060471340606281</v>
       </c>
-      <c r="AA40" s="9">
+      <c r="AA40" s="7">
         <v>20.906376342454529</v>
       </c>
-      <c r="AB40" s="9">
+      <c r="AB40" s="7">
         <v>20.8893894884182</v>
       </c>
-      <c r="AC40" s="9">
+      <c r="AC40" s="7">
         <v>21.207156295146969</v>
       </c>
-      <c r="AD40" s="9">
+      <c r="AD40" s="7">
         <v>21.19125940247438</v>
       </c>
-      <c r="AE40" s="9">
+      <c r="AE40" s="7">
         <v>22.667963719663739</v>
       </c>
-      <c r="AF40" s="9">
+      <c r="AF40" s="7">
         <v>27.914485963709119</v>
       </c>
-      <c r="AG40" s="9">
+      <c r="AG40" s="7">
         <v>45.480102512079448</v>
       </c>
-      <c r="AH40" s="9">
+      <c r="AH40" s="7">
         <v>43.517962735560417</v>
       </c>
-      <c r="AI40" s="9">
+      <c r="AI40" s="7">
         <v>23.369326266960321</v>
       </c>
-      <c r="AJ40" s="9">
+      <c r="AJ40" s="7">
         <v>23.40559561609399</v>
       </c>
-      <c r="AK40" s="9">
+      <c r="AK40" s="7">
         <v>27.324978618466432</v>
       </c>
-      <c r="AL40" s="9">
+      <c r="AL40" s="7">
         <v>24.772889596784601</v>
       </c>
     </row>
     <row r="41" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41" s="7">
         <v>5.5</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="7">
         <v>25.848196354336199</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="7">
         <v>25.820905679642031</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="7">
         <v>25.642895814490512</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="7">
         <v>25.534900489788569</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="7">
         <v>23.14566048749743</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="7">
         <v>23.378796382813348</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="7">
         <v>22.751483311533761</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="7">
         <v>23.32085518892816</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="7">
         <v>25.5038376520166</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="7">
         <v>25.472917692216861</v>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="7">
         <v>25.217095357890582</v>
       </c>
-      <c r="M41" s="9">
+      <c r="M41" s="7">
         <v>25.15253989030932</v>
       </c>
-      <c r="N41" s="9">
+      <c r="N41" s="7">
         <v>29.652951319878259</v>
       </c>
-      <c r="O41" s="9">
+      <c r="O41" s="7">
         <v>23.311356211034031</v>
       </c>
-      <c r="P41" s="9">
+      <c r="P41" s="7">
         <v>32.619544853409998</v>
       </c>
-      <c r="Q41" s="9">
+      <c r="Q41" s="7">
         <v>23.848802076049129</v>
       </c>
-      <c r="R41" s="9">
+      <c r="R41" s="7">
         <v>23.779131752382149</v>
       </c>
-      <c r="S41" s="9">
+      <c r="S41" s="7">
         <v>24.653556627762921</v>
       </c>
-      <c r="T41" s="9">
+      <c r="T41" s="7">
         <v>24.80477758877165</v>
       </c>
-      <c r="U41" s="9">
+      <c r="U41" s="7">
         <v>23.586026189605459</v>
       </c>
-      <c r="V41" s="9">
+      <c r="V41" s="7">
         <v>23.384107648740549</v>
       </c>
-      <c r="W41" s="9">
+      <c r="W41" s="7">
         <v>24.05493026049076</v>
       </c>
-      <c r="X41" s="9">
+      <c r="X41" s="7">
         <v>23.939850502148751</v>
       </c>
-      <c r="Y41" s="9">
+      <c r="Y41" s="7">
         <v>21.26810823524557</v>
       </c>
-      <c r="Z41" s="9">
+      <c r="Z41" s="7">
         <v>21.224026424840481</v>
       </c>
-      <c r="AA41" s="9">
+      <c r="AA41" s="7">
         <v>21.06745200538592</v>
       </c>
-      <c r="AB41" s="9">
+      <c r="AB41" s="7">
         <v>21.04920380930945</v>
       </c>
-      <c r="AC41" s="9">
+      <c r="AC41" s="7">
         <v>21.352063436652479</v>
       </c>
-      <c r="AD41" s="9">
+      <c r="AD41" s="7">
         <v>21.336813541458699</v>
       </c>
-      <c r="AE41" s="9">
+      <c r="AE41" s="7">
         <v>22.793866556273962</v>
       </c>
-      <c r="AF41" s="9">
+      <c r="AF41" s="7">
         <v>27.679128556974661</v>
       </c>
-      <c r="AG41" s="9">
+      <c r="AG41" s="7">
         <v>48.54706905381579</v>
       </c>
-      <c r="AH41" s="9">
+      <c r="AH41" s="7">
         <v>46.362503502062822</v>
       </c>
-      <c r="AI41" s="9">
+      <c r="AI41" s="7">
         <v>23.013730779224691</v>
       </c>
-      <c r="AJ41" s="9">
+      <c r="AJ41" s="7">
         <v>22.999941360238921</v>
       </c>
-      <c r="AK41" s="9">
+      <c r="AK41" s="7">
         <v>27.650988054522472</v>
       </c>
-      <c r="AL41" s="9">
+      <c r="AL41" s="7">
         <v>23.670830880670401</v>
       </c>
     </row>
     <row r="42" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A42" s="9">
+      <c r="A42" s="7">
         <v>6</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="7">
         <v>25.732294368858611</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="7">
         <v>25.726418893144221</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="7">
         <v>26.245545939552031</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="7">
         <v>26.140267379420909</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="7">
         <v>24.05005878447469</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="7">
         <v>23.977555089296679</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="7">
         <v>23.62643989996204</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="7">
         <v>23.691444355067091</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="7">
         <v>25.66425831166902</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="7">
         <v>25.623493570080019</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="7">
         <v>25.0013637089084</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="7">
         <v>25.028941766481491</v>
       </c>
-      <c r="N42" s="9">
+      <c r="N42" s="7">
         <v>30.83248433190365</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="7">
         <v>23.53225161970034</v>
       </c>
-      <c r="P42" s="9">
+      <c r="P42" s="7">
         <v>32.974179816844448</v>
       </c>
-      <c r="Q42" s="9">
+      <c r="Q42" s="7">
         <v>23.858228181321952</v>
       </c>
-      <c r="R42" s="9">
+      <c r="R42" s="7">
         <v>23.79789978218292</v>
       </c>
-      <c r="S42" s="9">
+      <c r="S42" s="7">
         <v>24.929159493357229</v>
       </c>
-      <c r="T42" s="9">
+      <c r="T42" s="7">
         <v>24.524778537843659</v>
       </c>
-      <c r="U42" s="9">
+      <c r="U42" s="7">
         <v>23.748687155411201</v>
       </c>
-      <c r="V42" s="9">
+      <c r="V42" s="7">
         <v>23.606326081320951</v>
       </c>
-      <c r="W42" s="9">
+      <c r="W42" s="7">
         <v>24.011256933634211</v>
       </c>
-      <c r="X42" s="9">
+      <c r="X42" s="7">
         <v>23.951928611178818</v>
       </c>
-      <c r="Y42" s="9">
+      <c r="Y42" s="7">
         <v>21.370177566471661</v>
       </c>
-      <c r="Z42" s="9">
+      <c r="Z42" s="7">
         <v>21.31530979149916</v>
       </c>
-      <c r="AA42" s="9">
+      <c r="AA42" s="7">
         <v>21.14765127987144</v>
       </c>
-      <c r="AB42" s="9">
+      <c r="AB42" s="7">
         <v>21.129307469266109</v>
       </c>
-      <c r="AC42" s="9">
+      <c r="AC42" s="7">
         <v>21.458485154822149</v>
       </c>
-      <c r="AD42" s="9">
+      <c r="AD42" s="7">
         <v>21.43916615344828</v>
       </c>
-      <c r="AE42" s="9">
+      <c r="AE42" s="7">
         <v>22.907125979834809</v>
       </c>
-      <c r="AF42" s="9">
+      <c r="AF42" s="7">
         <v>27.422636471122559</v>
       </c>
-      <c r="AG42" s="9">
+      <c r="AG42" s="7">
         <v>40.961573862517369</v>
       </c>
-      <c r="AH42" s="9">
+      <c r="AH42" s="7">
         <v>39.443653401858818</v>
       </c>
-      <c r="AI42" s="9">
+      <c r="AI42" s="7">
         <v>23.129032326024952</v>
       </c>
-      <c r="AJ42" s="9">
+      <c r="AJ42" s="7">
         <v>23.110456595580722</v>
       </c>
-      <c r="AK42" s="9">
+      <c r="AK42" s="7">
         <v>27.902712643659289</v>
       </c>
-      <c r="AL42" s="9">
+      <c r="AL42" s="7">
         <v>23.892865531660579</v>
       </c>
     </row>
     <row r="43" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
+      <c r="A43" s="7">
         <v>6.5</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="7">
         <v>26.163902846290611</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="7">
         <v>26.09835020457767</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="7">
         <v>26.314168290951852</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="7">
         <v>26.284204519193249</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="7">
         <v>23.90107696971862</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="7">
         <v>23.875431230424581</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="7">
         <v>25.2666116409262</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="7">
         <v>25.056988906322388</v>
       </c>
-      <c r="J43" s="9">
+      <c r="J43" s="7">
         <v>25.838984673622299</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="7">
         <v>25.812188065747929</v>
       </c>
-      <c r="L43" s="9">
+      <c r="L43" s="7">
         <v>25.220151373783111</v>
       </c>
-      <c r="M43" s="9">
+      <c r="M43" s="7">
         <v>25.186161239631939</v>
       </c>
-      <c r="N43" s="9">
+      <c r="N43" s="7">
         <v>27.117316144586709</v>
       </c>
-      <c r="O43" s="9">
+      <c r="O43" s="7">
         <v>23.765666781230198</v>
       </c>
-      <c r="P43" s="9">
+      <c r="P43" s="7">
         <v>33.728156807318641</v>
       </c>
-      <c r="Q43" s="9">
+      <c r="Q43" s="7">
         <v>23.628073690504309</v>
       </c>
-      <c r="R43" s="9">
+      <c r="R43" s="7">
         <v>23.677832306294761</v>
       </c>
-      <c r="S43" s="9">
+      <c r="S43" s="7">
         <v>25.748053290049459</v>
       </c>
-      <c r="T43" s="9">
+      <c r="T43" s="7">
         <v>24.5840108907726</v>
       </c>
-      <c r="U43" s="9">
+      <c r="U43" s="7">
         <v>24.122611013615419</v>
       </c>
-      <c r="V43" s="9">
+      <c r="V43" s="7">
         <v>23.81844900382707</v>
       </c>
-      <c r="W43" s="9">
+      <c r="W43" s="7">
         <v>23.692446087736919</v>
       </c>
-      <c r="X43" s="9">
+      <c r="X43" s="7">
         <v>23.745130763220981</v>
       </c>
-      <c r="Y43" s="9">
+      <c r="Y43" s="7">
         <v>21.489475171696011</v>
       </c>
-      <c r="Z43" s="9">
+      <c r="Z43" s="7">
         <v>21.418392403743471</v>
       </c>
-      <c r="AA43" s="9">
+      <c r="AA43" s="7">
         <v>21.238806475132691</v>
       </c>
-      <c r="AB43" s="9">
+      <c r="AB43" s="7">
         <v>21.219228925221842</v>
       </c>
-      <c r="AC43" s="9">
+      <c r="AC43" s="7">
         <v>21.567691119791451</v>
       </c>
-      <c r="AD43" s="9">
+      <c r="AD43" s="7">
         <v>21.542967662092099</v>
       </c>
-      <c r="AE43" s="9">
+      <c r="AE43" s="7">
         <v>23.034693209620411</v>
       </c>
-      <c r="AF43" s="9">
+      <c r="AF43" s="7">
         <v>27.529911140813422</v>
       </c>
-      <c r="AG43" s="9">
+      <c r="AG43" s="7">
         <v>38.327187752370143</v>
       </c>
-      <c r="AH43" s="9">
+      <c r="AH43" s="7">
         <v>37.034279120713101</v>
       </c>
-      <c r="AI43" s="9">
+      <c r="AI43" s="7">
         <v>23.552547763148141</v>
       </c>
-      <c r="AJ43" s="9">
+      <c r="AJ43" s="7">
         <v>23.529539571714619</v>
       </c>
-      <c r="AK43" s="9">
+      <c r="AK43" s="7">
         <v>28.080295959051089</v>
       </c>
-      <c r="AL43" s="9">
+      <c r="AL43" s="7">
         <v>23.973622878332272</v>
       </c>
     </row>
     <row r="44" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A44" s="9">
+      <c r="A44" s="7">
         <v>7</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="7">
         <v>25.98822107214901</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="7">
         <v>25.988271894821171</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="7">
         <v>25.564455272286871</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="7">
         <v>25.64710330327792</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="7">
         <v>26.448960940658921</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="7">
         <v>26.142873663661739</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="7">
         <v>22.834375019497699</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="7">
         <v>23.090546545531609</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="7">
         <v>25.89031255670622</v>
       </c>
-      <c r="K44" s="9">
+      <c r="K44" s="7">
         <v>25.87000805880664</v>
       </c>
-      <c r="L44" s="9">
+      <c r="L44" s="7">
         <v>26.356721759895049</v>
       </c>
-      <c r="M44" s="9">
+      <c r="M44" s="7">
         <v>26.22910576397911</v>
       </c>
-      <c r="N44" s="9">
+      <c r="N44" s="7">
         <v>30.112452808135309</v>
       </c>
-      <c r="O44" s="9">
+      <c r="O44" s="7">
         <v>24.006143752451699</v>
       </c>
-      <c r="P44" s="9">
+      <c r="P44" s="7">
         <v>33.957579714997223</v>
       </c>
-      <c r="Q44" s="9">
+      <c r="Q44" s="7">
         <v>24.60924188899795</v>
       </c>
-      <c r="R44" s="9">
+      <c r="R44" s="7">
         <v>24.368924808389771</v>
       </c>
-      <c r="S44" s="9">
+      <c r="S44" s="7">
         <v>24.929876140307009</v>
       </c>
-      <c r="T44" s="9">
+      <c r="T44" s="7">
         <v>25.191214157580049</v>
       </c>
-      <c r="U44" s="9">
+      <c r="U44" s="7">
         <v>23.919772642891349</v>
       </c>
-      <c r="V44" s="9">
+      <c r="V44" s="7">
         <v>23.91306134082199</v>
       </c>
-      <c r="W44" s="9">
+      <c r="W44" s="7">
         <v>24.541673665832139</v>
       </c>
-      <c r="X44" s="9">
+      <c r="X44" s="7">
         <v>24.35780611215306</v>
       </c>
-      <c r="Y44" s="9">
+      <c r="Y44" s="7">
         <v>21.640982947778109</v>
       </c>
-      <c r="Z44" s="9">
+      <c r="Z44" s="7">
         <v>21.584080230763639</v>
       </c>
-      <c r="AA44" s="9">
+      <c r="AA44" s="7">
         <v>21.39275664563085</v>
       </c>
-      <c r="AB44" s="9">
+      <c r="AB44" s="7">
         <v>21.371094587026629</v>
       </c>
-      <c r="AC44" s="9">
+      <c r="AC44" s="7">
         <v>21.71661701030196</v>
       </c>
-      <c r="AD44" s="9">
+      <c r="AD44" s="7">
         <v>21.699092232709329</v>
       </c>
-      <c r="AE44" s="9">
+      <c r="AE44" s="7">
         <v>23.175161050990472</v>
       </c>
-      <c r="AF44" s="9">
+      <c r="AF44" s="7">
         <v>27.359490341221971</v>
       </c>
-      <c r="AG44" s="9">
+      <c r="AG44" s="7">
         <v>43.196983927696778</v>
       </c>
-      <c r="AH44" s="9">
+      <c r="AH44" s="7">
         <v>41.492226117727988</v>
       </c>
-      <c r="AI44" s="9">
+      <c r="AI44" s="7">
         <v>23.155407895706819</v>
       </c>
-      <c r="AJ44" s="9">
+      <c r="AJ44" s="7">
         <v>23.132946597079659</v>
       </c>
-      <c r="AK44" s="9">
+      <c r="AK44" s="7">
         <v>28.14799071989458</v>
       </c>
-      <c r="AL44" s="9">
+      <c r="AL44" s="7">
         <v>25.46616778605976</v>
       </c>
     </row>
     <row r="45" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
+      <c r="A45" s="7">
         <v>7.5</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="7">
         <v>26.5882893392378</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="7">
         <v>26.508374610446491</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="7">
         <v>26.285604407358012</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="7">
         <v>26.21145091425473</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="7">
         <v>26.78185831886276</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="7">
         <v>26.70373887610857</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="7">
         <v>26.266540271072969</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="7">
         <v>25.87261298811633</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="7">
         <v>26.2236654843413</v>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="7">
         <v>26.17260386679072</v>
       </c>
-      <c r="L45" s="9">
+      <c r="L45" s="7">
         <v>26.924926304452299</v>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="7">
         <v>26.835489371241341</v>
       </c>
-      <c r="N45" s="9">
+      <c r="N45" s="7">
         <v>32.536704513653561</v>
       </c>
-      <c r="O45" s="9">
+      <c r="O45" s="7">
         <v>24.229350151002389</v>
       </c>
-      <c r="P45" s="9">
+      <c r="P45" s="7">
         <v>34.077557945604802</v>
       </c>
-      <c r="Q45" s="9">
+      <c r="Q45" s="7">
         <v>24.826432638462109</v>
       </c>
-      <c r="R45" s="9">
+      <c r="R45" s="7">
         <v>24.572205099437181</v>
       </c>
-      <c r="S45" s="9">
+      <c r="S45" s="7">
         <v>25.639272110547981</v>
       </c>
-      <c r="T45" s="9">
+      <c r="T45" s="7">
         <v>24.99952712679384</v>
       </c>
-      <c r="U45" s="9">
+      <c r="U45" s="7">
         <v>24.274605110988979</v>
       </c>
-      <c r="V45" s="9">
+      <c r="V45" s="7">
         <v>24.218524435145451</v>
       </c>
-      <c r="W45" s="9">
+      <c r="W45" s="7">
         <v>24.57071519087739</v>
       </c>
-      <c r="X45" s="9">
+      <c r="X45" s="7">
         <v>24.471098509702681</v>
       </c>
-      <c r="Y45" s="9">
+      <c r="Y45" s="7">
         <v>21.743517826529349</v>
       </c>
-      <c r="Z45" s="9">
+      <c r="Z45" s="7">
         <v>21.677970249522609</v>
       </c>
-      <c r="AA45" s="9">
+      <c r="AA45" s="7">
         <v>21.467372945915379</v>
       </c>
-      <c r="AB45" s="9">
+      <c r="AB45" s="7">
         <v>21.44170912438365</v>
       </c>
-      <c r="AC45" s="9">
+      <c r="AC45" s="7">
         <v>21.830685075203199</v>
       </c>
-      <c r="AD45" s="9">
+      <c r="AD45" s="7">
         <v>21.804847300592218</v>
       </c>
-      <c r="AE45" s="9">
+      <c r="AE45" s="7">
         <v>23.316181149788889</v>
       </c>
-      <c r="AF45" s="9">
+      <c r="AF45" s="7">
         <v>27.3479059774353</v>
       </c>
-      <c r="AG45" s="9">
+      <c r="AG45" s="7">
         <v>32.289965607466982</v>
       </c>
-      <c r="AH45" s="9">
+      <c r="AH45" s="7">
         <v>31.534158872812359</v>
       </c>
-      <c r="AI45" s="9">
+      <c r="AI45" s="7">
         <v>23.551261204748052</v>
       </c>
-      <c r="AJ45" s="9">
+      <c r="AJ45" s="7">
         <v>23.541592506150948</v>
       </c>
-      <c r="AK45" s="9">
+      <c r="AK45" s="7">
         <v>28.829476437479311</v>
       </c>
-      <c r="AL45" s="9">
+      <c r="AL45" s="7">
         <v>26.12098355602425</v>
       </c>
     </row>
     <row r="46" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
+      <c r="A46" s="7">
         <v>8</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="7">
         <v>27.275882466753391</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="7">
         <v>27.18389605678675</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="7">
         <v>26.308077039383619</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="7">
         <v>26.289938300517111</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="7">
         <v>27.663842223235939</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="7">
         <v>27.55990548685951</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="7">
         <v>28.445767358731931</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="7">
         <v>28.008370135144808</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="7">
         <v>26.702752995770179</v>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="7">
         <v>26.652898861161422</v>
       </c>
-      <c r="L46" s="9">
+      <c r="L46" s="7">
         <v>27.418777089775521</v>
       </c>
-      <c r="M46" s="9">
+      <c r="M46" s="7">
         <v>27.339995860611769</v>
       </c>
-      <c r="N46" s="9">
+      <c r="N46" s="7">
         <v>30.951188658913981</v>
       </c>
-      <c r="O46" s="9">
+      <c r="O46" s="7">
         <v>24.56629858535587</v>
       </c>
-      <c r="P46" s="9">
+      <c r="P46" s="7">
         <v>34.818726869951732</v>
       </c>
-      <c r="Q46" s="9">
+      <c r="Q46" s="7">
         <v>24.512871517329629</v>
       </c>
-      <c r="R46" s="9">
+      <c r="R46" s="7">
         <v>24.534807342661011</v>
       </c>
-      <c r="S46" s="9">
+      <c r="S46" s="7">
         <v>25.897971650226278</v>
       </c>
-      <c r="T46" s="9">
+      <c r="T46" s="7">
         <v>25.477855613170771</v>
       </c>
-      <c r="U46" s="9">
+      <c r="U46" s="7">
         <v>24.357639251602318</v>
       </c>
-      <c r="V46" s="9">
+      <c r="V46" s="7">
         <v>24.256833591735699</v>
       </c>
-      <c r="W46" s="9">
+      <c r="W46" s="7">
         <v>24.339717965862722</v>
       </c>
-      <c r="X46" s="9">
+      <c r="X46" s="7">
         <v>24.373937018049102</v>
       </c>
-      <c r="Y46" s="9">
+      <c r="Y46" s="7">
         <v>21.86802946220854</v>
       </c>
-      <c r="Z46" s="9">
+      <c r="Z46" s="7">
         <v>21.812602432152069</v>
       </c>
-      <c r="AA46" s="9">
+      <c r="AA46" s="7">
         <v>21.585997888862629</v>
       </c>
-      <c r="AB46" s="9">
+      <c r="AB46" s="7">
         <v>21.557039415501968</v>
       </c>
-      <c r="AC46" s="9">
+      <c r="AC46" s="7">
         <v>21.970882239779769</v>
       </c>
-      <c r="AD46" s="9">
+      <c r="AD46" s="7">
         <v>21.948739699794409</v>
       </c>
-      <c r="AE46" s="9">
+      <c r="AE46" s="7">
         <v>23.567210297793721</v>
       </c>
-      <c r="AF46" s="9">
+      <c r="AF46" s="7">
         <v>27.978633799075858</v>
       </c>
-      <c r="AG46" s="9">
+      <c r="AG46" s="7">
         <v>35.343680687724763</v>
       </c>
-      <c r="AH46" s="9">
+      <c r="AH46" s="7">
         <v>34.326926238162208</v>
       </c>
-      <c r="AI46" s="9">
+      <c r="AI46" s="7">
         <v>23.768803038521611</v>
       </c>
-      <c r="AJ46" s="9">
+      <c r="AJ46" s="7">
         <v>23.788918099052271</v>
       </c>
-      <c r="AK46" s="9">
+      <c r="AK46" s="7">
         <v>28.769835688144688</v>
       </c>
-      <c r="AL46" s="9">
+      <c r="AL46" s="7">
         <v>26.94185082772092</v>
       </c>
     </row>
     <row r="47" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
+      <c r="A47" s="7">
         <v>8.5</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="7">
         <v>27.051342610212291</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="7">
         <v>27.098606062726759</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="7">
         <v>26.47087719777014</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="7">
         <v>26.464472098899051</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="7">
         <v>26.33802759530225</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="7">
         <v>26.52008282761501</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="7">
         <v>27.042931434316952</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="7">
         <v>27.083820448083699</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="7">
         <v>26.992812975795221</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="7">
         <v>26.965081137284869</v>
       </c>
-      <c r="L47" s="9">
+      <c r="L47" s="7">
         <v>27.701913573246721</v>
       </c>
-      <c r="M47" s="9">
+      <c r="M47" s="7">
         <v>27.72133121248913</v>
       </c>
-      <c r="N47" s="9">
+      <c r="N47" s="7">
         <v>28.559575104103029</v>
       </c>
-      <c r="O47" s="9">
+      <c r="O47" s="7">
         <v>24.858443378250179</v>
       </c>
-      <c r="P47" s="9">
+      <c r="P47" s="7">
         <v>35.335606050908567</v>
       </c>
-      <c r="Q47" s="9">
+      <c r="Q47" s="7">
         <v>25.13008610641155</v>
       </c>
-      <c r="R47" s="9">
+      <c r="R47" s="7">
         <v>25.077914726818459</v>
       </c>
-      <c r="S47" s="9">
+      <c r="S47" s="7">
         <v>25.334866841616321</v>
       </c>
-      <c r="T47" s="9">
+      <c r="T47" s="7">
         <v>25.56576143153703</v>
       </c>
-      <c r="U47" s="9">
+      <c r="U47" s="7">
         <v>24.177210349819831</v>
       </c>
-      <c r="V47" s="9">
+      <c r="V47" s="7">
         <v>24.092981698890991</v>
       </c>
-      <c r="W47" s="9">
+      <c r="W47" s="7">
         <v>25.202523049214861</v>
       </c>
-      <c r="X47" s="9">
+      <c r="X47" s="7">
         <v>25.082950767621831</v>
       </c>
-      <c r="Y47" s="9">
+      <c r="Y47" s="7">
         <v>21.987523490267009</v>
       </c>
-      <c r="Z47" s="9">
+      <c r="Z47" s="7">
         <v>21.951876329741289</v>
       </c>
-      <c r="AA47" s="9">
+      <c r="AA47" s="7">
         <v>21.717064343297672</v>
       </c>
-      <c r="AB47" s="9">
+      <c r="AB47" s="7">
         <v>21.686491180146579</v>
       </c>
-      <c r="AC47" s="9">
+      <c r="AC47" s="7">
         <v>22.09644468574032</v>
       </c>
-      <c r="AD47" s="9">
+      <c r="AD47" s="7">
         <v>22.086077895843609</v>
       </c>
-      <c r="AE47" s="9">
+      <c r="AE47" s="7">
         <v>23.731929254556039</v>
       </c>
-      <c r="AF47" s="9">
+      <c r="AF47" s="7">
         <v>28.247210647759811</v>
       </c>
-      <c r="AG47" s="9">
+      <c r="AG47" s="7">
         <v>40.544619193956137</v>
       </c>
-      <c r="AH47" s="9">
+      <c r="AH47" s="7">
         <v>39.094914030628637</v>
       </c>
-      <c r="AI47" s="9">
+      <c r="AI47" s="7">
         <v>23.347070083771531</v>
       </c>
-      <c r="AJ47" s="9">
+      <c r="AJ47" s="7">
         <v>23.372877397208139</v>
       </c>
-      <c r="AK47" s="9">
+      <c r="AK47" s="7">
         <v>28.060219524695931</v>
       </c>
-      <c r="AL47" s="9">
+      <c r="AL47" s="7">
         <v>26.49679470206781</v>
       </c>
     </row>
     <row r="48" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
+      <c r="A48" s="7">
         <v>9</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="7">
         <v>27.60944717040147</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="7">
         <v>27.58586594082384</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="7">
         <v>27.16597123676528</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="7">
         <v>27.086478758834971</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="7">
         <v>26.457113782296069</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="7">
         <v>26.535905052419981</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="7">
         <v>26.912585909689628</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="7">
         <v>26.91267625873623</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="7">
         <v>27.199692304886799</v>
       </c>
-      <c r="K48" s="9">
+      <c r="K48" s="7">
         <v>27.188577169626701</v>
       </c>
-      <c r="L48" s="9">
+      <c r="L48" s="7">
         <v>27.314684072069639</v>
       </c>
-      <c r="M48" s="9">
+      <c r="M48" s="7">
         <v>27.43077121960685</v>
       </c>
-      <c r="N48" s="9">
+      <c r="N48" s="7">
         <v>28.013022506212831</v>
       </c>
-      <c r="O48" s="9">
+      <c r="O48" s="7">
         <v>25.117839285062011</v>
       </c>
-      <c r="P48" s="9">
+      <c r="P48" s="7">
         <v>36.108339381180528</v>
       </c>
-      <c r="Q48" s="9">
+      <c r="Q48" s="7">
         <v>25.052125842156251</v>
       </c>
-      <c r="R48" s="9">
+      <c r="R48" s="7">
         <v>25.00235130266736</v>
       </c>
-      <c r="S48" s="9">
+      <c r="S48" s="7">
         <v>26.330284875298481</v>
       </c>
-      <c r="T48" s="9">
+      <c r="T48" s="7">
         <v>25.5833290200971</v>
       </c>
-      <c r="U48" s="9">
+      <c r="U48" s="7">
         <v>25.014203590157781</v>
       </c>
-      <c r="V48" s="9">
+      <c r="V48" s="7">
         <v>24.565076858357031</v>
       </c>
-      <c r="W48" s="9">
+      <c r="W48" s="7">
         <v>24.864805153642259</v>
       </c>
-      <c r="X48" s="9">
+      <c r="X48" s="7">
         <v>24.97259899201428</v>
       </c>
-      <c r="Y48" s="9">
+      <c r="Y48" s="7">
         <v>22.120125052992801</v>
       </c>
-      <c r="Z48" s="9">
+      <c r="Z48" s="7">
         <v>22.064839198246549</v>
       </c>
-      <c r="AA48" s="9">
+      <c r="AA48" s="7">
         <v>21.80878578329758</v>
       </c>
-      <c r="AB48" s="9">
+      <c r="AB48" s="7">
         <v>21.777733177141329</v>
       </c>
-      <c r="AC48" s="9">
+      <c r="AC48" s="7">
         <v>22.223871210288731</v>
       </c>
-      <c r="AD48" s="9">
+      <c r="AD48" s="7">
         <v>22.2067291446191</v>
       </c>
-      <c r="AE48" s="9">
+      <c r="AE48" s="7">
         <v>23.83958768788542</v>
       </c>
-      <c r="AF48" s="9">
+      <c r="AF48" s="7">
         <v>28.356157545363999</v>
       </c>
-      <c r="AG48" s="9">
+      <c r="AG48" s="7">
         <v>39.520024877742927</v>
       </c>
-      <c r="AH48" s="9">
+      <c r="AH48" s="7">
         <v>38.188019459049883</v>
       </c>
-      <c r="AI48" s="9">
+      <c r="AI48" s="7">
         <v>23.827697761280739</v>
       </c>
-      <c r="AJ48" s="9">
+      <c r="AJ48" s="7">
         <v>23.841082374377539</v>
       </c>
-      <c r="AK48" s="9">
+      <c r="AK48" s="7">
         <v>28.778087184442089</v>
       </c>
-      <c r="AL48" s="9">
+      <c r="AL48" s="7">
         <v>26.55560209902734</v>
       </c>
     </row>
     <row r="49" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A49" s="9">
+      <c r="A49" s="7">
         <v>9.5</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="7">
         <v>27.754539665902701</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="7">
         <v>27.75951595931463</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="7">
         <v>27.77962053693501</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="7">
         <v>27.71673059165542</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="7">
         <v>26.247132087025818</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="7">
         <v>26.35572436697419</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="7">
         <v>26.846960072944128</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="7">
         <v>26.831302294865591</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="7">
         <v>27.50764889732692</v>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="7">
         <v>27.484336465184469</v>
       </c>
-      <c r="L49" s="9">
+      <c r="L49" s="7">
         <v>27.985400951201051</v>
       </c>
-      <c r="M49" s="9">
+      <c r="M49" s="7">
         <v>27.940990930440829</v>
       </c>
-      <c r="N49" s="9">
+      <c r="N49" s="7">
         <v>32.454580127520842</v>
       </c>
-      <c r="O49" s="9">
+      <c r="O49" s="7">
         <v>25.377527989657221</v>
       </c>
-      <c r="P49" s="9">
+      <c r="P49" s="7">
         <v>36.284979621709333</v>
       </c>
-      <c r="Q49" s="9">
+      <c r="Q49" s="7">
         <v>25.316506688885749</v>
       </c>
-      <c r="R49" s="9">
+      <c r="R49" s="7">
         <v>25.24253195234078</v>
       </c>
-      <c r="S49" s="9">
+      <c r="S49" s="7">
         <v>26.153403046959689</v>
       </c>
-      <c r="T49" s="9">
+      <c r="T49" s="7">
         <v>26.153041319529869</v>
       </c>
-      <c r="U49" s="9">
+      <c r="U49" s="7">
         <v>25.031900265933199</v>
       </c>
-      <c r="V49" s="9">
+      <c r="V49" s="7">
         <v>24.751094796670621</v>
       </c>
-      <c r="W49" s="9">
+      <c r="W49" s="7">
         <v>24.94228252011397</v>
       </c>
-      <c r="X49" s="9">
+      <c r="X49" s="7">
         <v>25.025144072711289</v>
       </c>
-      <c r="Y49" s="9">
+      <c r="Y49" s="7">
         <v>22.22498994882789</v>
       </c>
-      <c r="Z49" s="9">
+      <c r="Z49" s="7">
         <v>22.17213223288455</v>
       </c>
-      <c r="AA49" s="9">
+      <c r="AA49" s="7">
         <v>21.904156498014149</v>
       </c>
-      <c r="AB49" s="9">
+      <c r="AB49" s="7">
         <v>21.870803786372012</v>
       </c>
-      <c r="AC49" s="9">
+      <c r="AC49" s="7">
         <v>22.34327276022757</v>
       </c>
-      <c r="AD49" s="9">
+      <c r="AD49" s="7">
         <v>22.32610898507242</v>
       </c>
-      <c r="AE49" s="9">
+      <c r="AE49" s="7">
         <v>24.002814935435421</v>
       </c>
-      <c r="AF49" s="9">
+      <c r="AF49" s="7">
         <v>28.653352687085501</v>
       </c>
-      <c r="AG49" s="9">
+      <c r="AG49" s="7">
         <v>37.511016921147032</v>
       </c>
-      <c r="AH49" s="9">
+      <c r="AH49" s="7">
         <v>36.363469746016847</v>
       </c>
-      <c r="AI49" s="9">
+      <c r="AI49" s="7">
         <v>23.68839103546922</v>
       </c>
-      <c r="AJ49" s="9">
+      <c r="AJ49" s="7">
         <v>23.703534217643782</v>
       </c>
-      <c r="AK49" s="9">
+      <c r="AK49" s="7">
         <v>29.211157838626949</v>
       </c>
-      <c r="AL49" s="9">
+      <c r="AL49" s="7">
         <v>26.328772780404361</v>
       </c>
     </row>
     <row r="50" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A50" s="9">
+      <c r="A50" s="7">
         <v>10</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="7">
         <v>28.392690728276609</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="7">
         <v>28.307212341339159</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="7">
         <v>28.589258859614251</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="7">
         <v>28.532128061895609</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="7">
         <v>26.701536378129319</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="7">
         <v>26.697398600968501</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="7">
         <v>26.249458221200701</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="7">
         <v>26.29518573131541</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="7">
         <v>27.5515853148456</v>
       </c>
-      <c r="K50" s="9">
+      <c r="K50" s="7">
         <v>27.53156203799983</v>
       </c>
-      <c r="L50" s="9">
+      <c r="L50" s="7">
         <v>28.516955598130561</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="7">
         <v>28.404094082505839</v>
       </c>
-      <c r="N50" s="9">
+      <c r="N50" s="7">
         <v>29.795466252882552</v>
       </c>
-      <c r="O50" s="9">
+      <c r="O50" s="7">
         <v>25.526348182711221</v>
       </c>
-      <c r="P50" s="9">
+      <c r="P50" s="7">
         <v>35.801838722673537</v>
       </c>
-      <c r="Q50" s="9">
+      <c r="Q50" s="7">
         <v>25.160118007052802</v>
       </c>
-      <c r="R50" s="9">
+      <c r="R50" s="7">
         <v>25.23564649784991</v>
       </c>
-      <c r="S50" s="9">
+      <c r="S50" s="7">
         <v>25.785872024484</v>
       </c>
-      <c r="T50" s="9">
+      <c r="T50" s="7">
         <v>26.861185061511971</v>
       </c>
-      <c r="U50" s="9">
+      <c r="U50" s="7">
         <v>25.116741818074718</v>
       </c>
-      <c r="V50" s="9">
+      <c r="V50" s="7">
         <v>24.744242913110771</v>
       </c>
-      <c r="W50" s="9">
+      <c r="W50" s="7">
         <v>25.05694797589344</v>
       </c>
-      <c r="X50" s="9">
+      <c r="X50" s="7">
         <v>25.191164357724119</v>
       </c>
-      <c r="Y50" s="9">
+      <c r="Y50" s="7">
         <v>22.318868111762932</v>
       </c>
-      <c r="Z50" s="9">
+      <c r="Z50" s="7">
         <v>22.267166136229129</v>
       </c>
-      <c r="AA50" s="9">
+      <c r="AA50" s="7">
         <v>21.984797033214679</v>
       </c>
-      <c r="AB50" s="9">
+      <c r="AB50" s="7">
         <v>21.947465860265101</v>
       </c>
-      <c r="AC50" s="9">
+      <c r="AC50" s="7">
         <v>22.44931544684373</v>
       </c>
-      <c r="AD50" s="9">
+      <c r="AD50" s="7">
         <v>22.427061442272461</v>
       </c>
-      <c r="AE50" s="9">
+      <c r="AE50" s="7">
         <v>24.04089616352616</v>
       </c>
-      <c r="AF50" s="9">
+      <c r="AF50" s="7">
         <v>28.734855628527239</v>
       </c>
-      <c r="AG50" s="9">
+      <c r="AG50" s="7">
         <v>31.764626632625859</v>
       </c>
-      <c r="AH50" s="9">
+      <c r="AH50" s="7">
         <v>31.122365247221719</v>
       </c>
-      <c r="AI50" s="9">
+      <c r="AI50" s="7">
         <v>23.513073346644379</v>
       </c>
-      <c r="AJ50" s="9">
+      <c r="AJ50" s="7">
         <v>23.52902305254522</v>
       </c>
-      <c r="AK50" s="9">
+      <c r="AK50" s="7">
         <v>28.802633834807761</v>
       </c>
-      <c r="AL50" s="9">
+      <c r="AL50" s="7">
         <v>26.64878874785704</v>
       </c>
     </row>
     <row r="51" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A51" s="9">
+      <c r="A51" s="7">
         <v>10.5</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="7">
         <v>28.574059343062348</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="7">
         <v>28.536983781212051</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="7">
         <v>28.781253560702059</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="7">
         <v>28.80401194132882</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="7">
         <v>24.852239742481821</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="7">
         <v>25.152810231764679</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="7">
         <v>25.34933093400695</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="7">
         <v>25.469682182551889</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="7">
         <v>27.711694886873111</v>
       </c>
-      <c r="K51" s="9">
+      <c r="K51" s="7">
         <v>27.68350848887173</v>
       </c>
-      <c r="L51" s="9">
+      <c r="L51" s="7">
         <v>28.417104409647269</v>
       </c>
-      <c r="M51" s="9">
+      <c r="M51" s="7">
         <v>28.387746163388041</v>
       </c>
-      <c r="N51" s="9">
+      <c r="N51" s="7">
         <v>33.954971655788661</v>
       </c>
-      <c r="O51" s="9">
+      <c r="O51" s="7">
         <v>25.727885484552079</v>
       </c>
-      <c r="P51" s="9">
+      <c r="P51" s="7">
         <v>35.881525106532088</v>
       </c>
-      <c r="Q51" s="9">
+      <c r="Q51" s="7">
         <v>25.5346021294378</v>
       </c>
-      <c r="R51" s="9">
+      <c r="R51" s="7">
         <v>25.440901183059012</v>
       </c>
-      <c r="S51" s="9">
+      <c r="S51" s="7">
         <v>25.95664817936267</v>
       </c>
-      <c r="T51" s="9">
+      <c r="T51" s="7">
         <v>26.587610080504462</v>
       </c>
-      <c r="U51" s="9">
+      <c r="U51" s="7">
         <v>25.41334108908546</v>
       </c>
-      <c r="V51" s="9">
+      <c r="V51" s="7">
         <v>25.05376376197291</v>
       </c>
-      <c r="W51" s="9">
+      <c r="W51" s="7">
         <v>25.25838050338804</v>
       </c>
-      <c r="X51" s="9">
+      <c r="X51" s="7">
         <v>25.387310321212698</v>
       </c>
-      <c r="Y51" s="9">
+      <c r="Y51" s="7">
         <v>22.434722402933549</v>
       </c>
-      <c r="Z51" s="9">
+      <c r="Z51" s="7">
         <v>22.373586435686079</v>
       </c>
-      <c r="AA51" s="9">
+      <c r="AA51" s="7">
         <v>22.08312173320822</v>
       </c>
-      <c r="AB51" s="9">
+      <c r="AB51" s="7">
         <v>22.04338718615783</v>
       </c>
-      <c r="AC51" s="9">
+      <c r="AC51" s="7">
         <v>22.564369474795861</v>
       </c>
-      <c r="AD51" s="9">
+      <c r="AD51" s="7">
         <v>22.53634745126244</v>
       </c>
-      <c r="AE51" s="9">
+      <c r="AE51" s="7">
         <v>24.13044283314753</v>
       </c>
-      <c r="AF51" s="9">
+      <c r="AF51" s="7">
         <v>28.504809202673041</v>
       </c>
-      <c r="AG51" s="9">
+      <c r="AG51" s="7">
         <v>35.037982574980518</v>
       </c>
-      <c r="AH51" s="9">
+      <c r="AH51" s="7">
         <v>34.123449052299897</v>
       </c>
-      <c r="AI51" s="9">
+      <c r="AI51" s="7">
         <v>23.400328029223729</v>
       </c>
-      <c r="AJ51" s="9">
+      <c r="AJ51" s="7">
         <v>23.39238528420001</v>
       </c>
-      <c r="AK51" s="9">
+      <c r="AK51" s="7">
         <v>29.358115920189999</v>
       </c>
-      <c r="AL51" s="9">
+      <c r="AL51" s="7">
         <v>25.61818999232262</v>
       </c>
     </row>
     <row r="52" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A52" s="9">
+      <c r="A52" s="7">
         <v>11</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="7">
         <v>28.829815733828148</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="7">
         <v>28.86367806326167</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="7">
         <v>28.07252326248522</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="7">
         <v>28.259652045677921</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="7">
         <v>28.295189867388881</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="7">
         <v>27.970516340348549</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="7">
         <v>28.181724863387021</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="7">
         <v>27.807465298328889</v>
       </c>
-      <c r="J52" s="9">
+      <c r="J52" s="7">
         <v>28.25153834855336</v>
       </c>
-      <c r="K52" s="9">
+      <c r="K52" s="7">
         <v>28.215876970754721</v>
       </c>
-      <c r="L52" s="9">
+      <c r="L52" s="7">
         <v>28.78391302396474</v>
       </c>
-      <c r="M52" s="9">
+      <c r="M52" s="7">
         <v>28.777568585272679</v>
       </c>
-      <c r="N52" s="9">
+      <c r="N52" s="7">
         <v>35.282668511934212</v>
       </c>
-      <c r="O52" s="9">
+      <c r="O52" s="7">
         <v>26.092298275057541</v>
       </c>
-      <c r="P52" s="9">
+      <c r="P52" s="7">
         <v>36.650189722732627</v>
       </c>
-      <c r="Q52" s="9">
+      <c r="Q52" s="7">
         <v>26.21842354163952</v>
       </c>
-      <c r="R52" s="9">
+      <c r="R52" s="7">
         <v>26.05204408198755</v>
       </c>
-      <c r="S52" s="9">
+      <c r="S52" s="7">
         <v>26.561233747973919</v>
       </c>
-      <c r="T52" s="9">
+      <c r="T52" s="7">
         <v>26.914859025693431</v>
       </c>
-      <c r="U52" s="9">
+      <c r="U52" s="7">
         <v>25.690370301920002</v>
       </c>
-      <c r="V52" s="9">
+      <c r="V52" s="7">
         <v>25.26343815161384</v>
       </c>
-      <c r="W52" s="9">
+      <c r="W52" s="7">
         <v>26.004630563842529</v>
       </c>
-      <c r="X52" s="9">
+      <c r="X52" s="7">
         <v>26.062253478756791</v>
       </c>
-      <c r="Y52" s="9">
+      <c r="Y52" s="7">
         <v>22.56446855048403</v>
       </c>
-      <c r="Z52" s="9">
+      <c r="Z52" s="7">
         <v>22.507690069249978</v>
       </c>
-      <c r="AA52" s="9">
+      <c r="AA52" s="7">
         <v>22.195294508491219</v>
       </c>
-      <c r="AB52" s="9">
+      <c r="AB52" s="7">
         <v>22.154648040836651</v>
       </c>
-      <c r="AC52" s="9">
+      <c r="AC52" s="7">
         <v>22.718238188592949</v>
       </c>
-      <c r="AD52" s="9">
+      <c r="AD52" s="7">
         <v>22.692706677306109</v>
       </c>
-      <c r="AE52" s="9">
+      <c r="AE52" s="7">
         <v>24.39796008177354</v>
       </c>
-      <c r="AF52" s="9">
+      <c r="AF52" s="7">
         <v>28.997010396551161</v>
       </c>
-      <c r="AG52" s="9">
+      <c r="AG52" s="7">
         <v>39.073500293239711</v>
       </c>
-      <c r="AH52" s="9">
+      <c r="AH52" s="7">
         <v>37.836669462100282</v>
       </c>
-      <c r="AI52" s="9">
+      <c r="AI52" s="7">
         <v>23.85034144193212</v>
       </c>
-      <c r="AJ52" s="9">
+      <c r="AJ52" s="7">
         <v>23.876465214391889</v>
       </c>
-      <c r="AK52" s="9">
+      <c r="AK52" s="7">
         <v>29.819142612871119</v>
       </c>
-      <c r="AL52" s="9">
+      <c r="AL52" s="7">
         <v>27.301791013394041</v>
       </c>
     </row>
     <row r="53" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A53" s="9">
+      <c r="A53" s="7">
         <v>11.5</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="7">
         <v>29.383918864425929</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="7">
         <v>29.3300884780835</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="7">
         <v>29.25372231497925</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="7">
         <v>29.232755035377981</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="7">
         <v>26.45691984384738</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="7">
         <v>26.631059079647081</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="7">
         <v>27.198892585002351</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="7">
         <v>27.171403975035361</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="7">
         <v>28.235385449588058</v>
       </c>
-      <c r="K53" s="9">
+      <c r="K53" s="7">
         <v>28.22843152701434</v>
       </c>
-      <c r="L53" s="9">
+      <c r="L53" s="7">
         <v>29.417303406940491</v>
       </c>
-      <c r="M53" s="9">
+      <c r="M53" s="7">
         <v>29.284219413045889</v>
       </c>
-      <c r="N53" s="9">
+      <c r="N53" s="7">
         <v>27.96224248095869</v>
       </c>
-      <c r="O53" s="9">
+      <c r="O53" s="7">
         <v>26.227796726544231</v>
       </c>
-      <c r="P53" s="9">
+      <c r="P53" s="7">
         <v>36.400417441076783</v>
       </c>
-      <c r="Q53" s="9">
+      <c r="Q53" s="7">
         <v>26.18595887817288</v>
       </c>
-      <c r="R53" s="9">
+      <c r="R53" s="7">
         <v>26.011208497027749</v>
       </c>
-      <c r="S53" s="9">
+      <c r="S53" s="7">
         <v>26.53734254255361</v>
       </c>
-      <c r="T53" s="9">
+      <c r="T53" s="7">
         <v>27.68347920215302</v>
       </c>
-      <c r="U53" s="9">
+      <c r="U53" s="7">
         <v>25.963524850926991</v>
       </c>
-      <c r="V53" s="9">
+      <c r="V53" s="7">
         <v>25.251442905250961</v>
       </c>
-      <c r="W53" s="9">
+      <c r="W53" s="7">
         <v>25.790975207290259</v>
       </c>
-      <c r="X53" s="9">
+      <c r="X53" s="7">
         <v>26.01882436290223</v>
       </c>
-      <c r="Y53" s="9">
+      <c r="Y53" s="7">
         <v>22.66805134784061</v>
       </c>
-      <c r="Z53" s="9">
+      <c r="Z53" s="7">
         <v>22.604871347360952</v>
       </c>
-      <c r="AA53" s="9">
+      <c r="AA53" s="7">
         <v>22.27796240917662</v>
       </c>
-      <c r="AB53" s="9">
+      <c r="AB53" s="7">
         <v>22.23314930472236</v>
       </c>
-      <c r="AC53" s="9">
+      <c r="AC53" s="7">
         <v>22.820398776639109</v>
       </c>
-      <c r="AD53" s="9">
+      <c r="AD53" s="7">
         <v>22.787895894426189</v>
       </c>
-      <c r="AE53" s="9">
+      <c r="AE53" s="7">
         <v>24.405208832949921</v>
       </c>
-      <c r="AF53" s="9">
+      <c r="AF53" s="7">
         <v>29.17026472220056</v>
       </c>
-      <c r="AG53" s="9">
+      <c r="AG53" s="7">
         <v>32.998006661330393</v>
       </c>
-      <c r="AH53" s="9">
+      <c r="AH53" s="7">
         <v>32.310903741816531</v>
       </c>
-      <c r="AI53" s="9">
+      <c r="AI53" s="7">
         <v>23.785228396415889</v>
       </c>
-      <c r="AJ53" s="9">
+      <c r="AJ53" s="7">
         <v>23.79672962212787</v>
       </c>
-      <c r="AK53" s="9">
+      <c r="AK53" s="7">
         <v>29.235946663516049</v>
       </c>
-      <c r="AL53" s="9">
+      <c r="AL53" s="7">
         <v>26.929139866376008</v>
       </c>
     </row>
     <row r="54" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A54" s="9">
+      <c r="A54" s="7">
         <v>12</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="7">
         <v>29.392469161886851</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="7">
         <v>29.469673437670689</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="7">
         <v>29.367047108612169</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="7">
         <v>29.467118809485271</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="7">
         <v>24.165459000720389</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="7">
         <v>24.58282701592562</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="7">
         <v>28.23261466943389</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="7">
         <v>28.054225645661781</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J54" s="7">
         <v>28.736237256271309</v>
       </c>
-      <c r="K54" s="9">
+      <c r="K54" s="7">
         <v>28.748109308971401</v>
       </c>
-      <c r="L54" s="9">
+      <c r="L54" s="7">
         <v>29.61234892503559</v>
       </c>
-      <c r="M54" s="9">
+      <c r="M54" s="7">
         <v>29.534813629694082</v>
       </c>
-      <c r="N54" s="9">
+      <c r="N54" s="7">
         <v>32.411034883318791</v>
       </c>
-      <c r="O54" s="9">
+      <c r="O54" s="7">
         <v>26.611385112240932</v>
       </c>
-      <c r="P54" s="9">
+      <c r="P54" s="7">
         <v>37.693125197339462</v>
       </c>
-      <c r="Q54" s="9">
+      <c r="Q54" s="7">
         <v>25.988494147829609</v>
       </c>
-      <c r="R54" s="9">
+      <c r="R54" s="7">
         <v>26.036985194299699</v>
       </c>
-      <c r="S54" s="9">
+      <c r="S54" s="7">
         <v>26.968474912605181</v>
       </c>
-      <c r="T54" s="9">
+      <c r="T54" s="7">
         <v>27.946950460833989</v>
       </c>
-      <c r="U54" s="9">
+      <c r="U54" s="7">
         <v>26.007371585110171</v>
       </c>
-      <c r="V54" s="9">
+      <c r="V54" s="7">
         <v>25.438466442334359</v>
       </c>
-      <c r="W54" s="9">
+      <c r="W54" s="7">
         <v>25.91399708034616</v>
       </c>
-      <c r="X54" s="9">
+      <c r="X54" s="7">
         <v>26.148880061679851</v>
       </c>
-      <c r="Y54" s="9">
+      <c r="Y54" s="7">
         <v>22.819794235919581</v>
       </c>
-      <c r="Z54" s="9">
+      <c r="Z54" s="7">
         <v>22.76349699551206</v>
       </c>
-      <c r="AA54" s="9">
+      <c r="AA54" s="7">
         <v>22.436048736693269</v>
       </c>
-      <c r="AB54" s="9">
+      <c r="AB54" s="7">
         <v>22.389619307691351</v>
       </c>
-      <c r="AC54" s="9">
+      <c r="AC54" s="7">
         <v>22.968062715304789</v>
       </c>
-      <c r="AD54" s="9">
+      <c r="AD54" s="7">
         <v>22.94402431344394</v>
       </c>
-      <c r="AE54" s="9">
+      <c r="AE54" s="7">
         <v>24.713894886584381</v>
       </c>
-      <c r="AF54" s="9">
+      <c r="AF54" s="7">
         <v>30.007511301125462</v>
       </c>
-      <c r="AG54" s="9">
+      <c r="AG54" s="7">
         <v>45.516461234870732</v>
       </c>
-      <c r="AH54" s="9">
+      <c r="AH54" s="7">
         <v>43.772447099646811</v>
       </c>
-      <c r="AI54" s="9">
+      <c r="AI54" s="7">
         <v>23.781777450296062</v>
       </c>
-      <c r="AJ54" s="9">
+      <c r="AJ54" s="7">
         <v>23.79261622458603</v>
       </c>
-      <c r="AK54" s="9">
+      <c r="AK54" s="7">
         <v>29.857786897509541</v>
       </c>
-      <c r="AL54" s="9">
+      <c r="AL54" s="7">
         <v>25.397570391343791</v>
       </c>
     </row>
     <row r="55" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A55" s="9">
+      <c r="A55" s="7">
         <v>12.5</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="7">
         <v>29.03376641370053</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="7">
         <v>29.190183040502991</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="7">
         <v>28.41677038568837</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="7">
         <v>28.694246988908269</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="7">
         <v>22.94874682323821</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="7">
         <v>23.233217310842971</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="7">
         <v>27.552872496156731</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="7">
         <v>27.54757323556915</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J55" s="7">
         <v>29.09758731098999</v>
       </c>
-      <c r="K55" s="9">
+      <c r="K55" s="7">
         <v>29.109656509530019</v>
       </c>
-      <c r="L55" s="9">
+      <c r="L55" s="7">
         <v>29.56417548255197</v>
       </c>
-      <c r="M55" s="9">
+      <c r="M55" s="7">
         <v>29.535687295941749</v>
       </c>
-      <c r="N55" s="9">
+      <c r="N55" s="7">
         <v>34.611652181903743</v>
       </c>
-      <c r="O55" s="9">
+      <c r="O55" s="7">
         <v>26.896884504778079</v>
       </c>
-      <c r="P55" s="9">
+      <c r="P55" s="7">
         <v>38.382988511295217</v>
       </c>
-      <c r="Q55" s="9">
+      <c r="Q55" s="7">
         <v>25.593644843144421</v>
       </c>
-      <c r="R55" s="9">
+      <c r="R55" s="7">
         <v>25.759936403577189</v>
       </c>
-      <c r="S55" s="9">
+      <c r="S55" s="7">
         <v>27.268165033462761</v>
       </c>
-      <c r="T55" s="9">
+      <c r="T55" s="7">
         <v>28.183705541517391</v>
       </c>
-      <c r="U55" s="9">
+      <c r="U55" s="7">
         <v>26.116728192152362</v>
       </c>
-      <c r="V55" s="9">
+      <c r="V55" s="7">
         <v>25.585781338978801</v>
       </c>
-      <c r="W55" s="9">
+      <c r="W55" s="7">
         <v>25.424535406090541</v>
       </c>
-      <c r="X55" s="9">
+      <c r="X55" s="7">
         <v>25.82717192070993</v>
       </c>
-      <c r="Y55" s="9">
+      <c r="Y55" s="7">
         <v>22.928309831460869</v>
       </c>
-      <c r="Z55" s="9">
+      <c r="Z55" s="7">
         <v>22.86553665990478</v>
       </c>
-      <c r="AA55" s="9">
+      <c r="AA55" s="7">
         <v>22.53613072610521</v>
       </c>
-      <c r="AB55" s="9">
+      <c r="AB55" s="7">
         <v>22.48880889031221</v>
       </c>
-      <c r="AC55" s="9">
+      <c r="AC55" s="7">
         <v>23.071876969982441</v>
       </c>
-      <c r="AD55" s="9">
+      <c r="AD55" s="7">
         <v>23.050170497222531</v>
       </c>
-      <c r="AE55" s="9">
+      <c r="AE55" s="7">
         <v>24.90960204218872</v>
       </c>
-      <c r="AF55" s="9">
+      <c r="AF55" s="7">
         <v>30.415969168521709</v>
       </c>
-      <c r="AG55" s="9">
+      <c r="AG55" s="7">
         <v>44.97541578760071</v>
       </c>
-      <c r="AH55" s="9">
+      <c r="AH55" s="7">
         <v>43.303984407881487</v>
       </c>
-      <c r="AI55" s="9">
+      <c r="AI55" s="7">
         <v>23.846759395364732</v>
       </c>
-      <c r="AJ55" s="9">
+      <c r="AJ55" s="7">
         <v>23.851879835477561</v>
       </c>
-      <c r="AK55" s="9">
+      <c r="AK55" s="7">
         <v>30.188189886601229</v>
       </c>
-      <c r="AL55" s="9">
+      <c r="AL55" s="7">
         <v>24.170012016908249</v>
       </c>
     </row>
     <row r="56" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A56" s="9">
+      <c r="A56" s="7">
         <v>13</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="7">
         <v>29.385342708350311</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="7">
         <v>29.399873282138</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="7">
         <v>28.993780431623719</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="7">
         <v>29.131407492851249</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="7">
         <v>22.632380359620569</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="7">
         <v>22.74595443246503</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="7">
         <v>24.26253970334264</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="7">
         <v>24.652533273577511</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J56" s="7">
         <v>28.9403854335722</v>
       </c>
-      <c r="K56" s="9">
+      <c r="K56" s="7">
         <v>28.935356322292439</v>
       </c>
-      <c r="L56" s="9">
+      <c r="L56" s="7">
         <v>29.758487794683798</v>
       </c>
-      <c r="M56" s="9">
+      <c r="M56" s="7">
         <v>29.761910572557031</v>
       </c>
-      <c r="N56" s="9">
+      <c r="N56" s="7">
         <v>35.355702542255237</v>
       </c>
-      <c r="O56" s="9">
+      <c r="O56" s="7">
         <v>26.9186688907456</v>
       </c>
-      <c r="P56" s="9">
+      <c r="P56" s="7">
         <v>37.189050048589301</v>
       </c>
-      <c r="Q56" s="9">
+      <c r="Q56" s="7">
         <v>25.914442407960539</v>
       </c>
-      <c r="R56" s="9">
+      <c r="R56" s="7">
         <v>25.94402672798169</v>
       </c>
-      <c r="S56" s="9">
+      <c r="S56" s="7">
         <v>26.436257979826859</v>
       </c>
-      <c r="T56" s="9">
+      <c r="T56" s="7">
         <v>27.635728343385981</v>
       </c>
-      <c r="U56" s="9">
+      <c r="U56" s="7">
         <v>25.992725653892851</v>
       </c>
-      <c r="V56" s="9">
+      <c r="V56" s="7">
         <v>25.579877043866059</v>
       </c>
-      <c r="W56" s="9">
+      <c r="W56" s="7">
         <v>25.855362883157579</v>
       </c>
-      <c r="X56" s="9">
+      <c r="X56" s="7">
         <v>26.153906549879029</v>
       </c>
-      <c r="Y56" s="9">
+      <c r="Y56" s="7">
         <v>22.997490760058909</v>
       </c>
-      <c r="Z56" s="9">
+      <c r="Z56" s="7">
         <v>22.925569106173828</v>
       </c>
-      <c r="AA56" s="9">
+      <c r="AA56" s="7">
         <v>22.594761834070411</v>
       </c>
-      <c r="AB56" s="9">
+      <c r="AB56" s="7">
         <v>22.54292405284875</v>
       </c>
-      <c r="AC56" s="9">
+      <c r="AC56" s="7">
         <v>23.134609525380821</v>
       </c>
-      <c r="AD56" s="9">
+      <c r="AD56" s="7">
         <v>23.103632995785841</v>
       </c>
-      <c r="AE56" s="9">
+      <c r="AE56" s="7">
         <v>24.79672590305578</v>
       </c>
-      <c r="AF56" s="9">
+      <c r="AF56" s="7">
         <v>29.519424280503511</v>
       </c>
-      <c r="AG56" s="9">
+      <c r="AG56" s="7">
         <v>32.748569105698607</v>
       </c>
-      <c r="AH56" s="9">
+      <c r="AH56" s="7">
         <v>32.133047296513823</v>
       </c>
-      <c r="AI56" s="9">
+      <c r="AI56" s="7">
         <v>23.404180827867901</v>
       </c>
-      <c r="AJ56" s="9">
+      <c r="AJ56" s="7">
         <v>23.38545213200069</v>
       </c>
-      <c r="AK56" s="9">
+      <c r="AK56" s="7">
         <v>29.890093504462019</v>
       </c>
-      <c r="AL56" s="9">
+      <c r="AL56" s="7">
         <v>23.601714248210559</v>
       </c>
     </row>
     <row r="57" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A57" s="9">
+      <c r="A57" s="7">
         <v>13.5</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="7">
         <v>29.869992726949182</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="7">
         <v>29.879167487426422</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="7">
         <v>29.10069864010185</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="7">
         <v>29.30074745695261</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="7">
         <v>22.493258614275678</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="7">
         <v>22.52371971012083</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="7">
         <v>24.178159093266629</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="7">
         <v>24.274615712916319</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="7">
         <v>28.84187557094884</v>
       </c>
-      <c r="K57" s="9">
+      <c r="K57" s="7">
         <v>28.894636734174981</v>
       </c>
-      <c r="L57" s="9">
+      <c r="L57" s="7">
         <v>29.194692608502621</v>
       </c>
-      <c r="M57" s="9">
+      <c r="M57" s="7">
         <v>29.33722413348379</v>
       </c>
-      <c r="N57" s="9">
+      <c r="N57" s="7">
         <v>28.33653888180686</v>
       </c>
-      <c r="O57" s="9">
+      <c r="O57" s="7">
         <v>27.11377294419103</v>
       </c>
-      <c r="P57" s="9">
+      <c r="P57" s="7">
         <v>37.693917144674089</v>
       </c>
-      <c r="Q57" s="9">
+      <c r="Q57" s="7">
         <v>26.01677539290559</v>
       </c>
-      <c r="R57" s="9">
+      <c r="R57" s="7">
         <v>25.918696703551571</v>
       </c>
-      <c r="S57" s="9">
+      <c r="S57" s="7">
         <v>26.545195951738659</v>
       </c>
-      <c r="T57" s="9">
+      <c r="T57" s="7">
         <v>27.249264254050999</v>
       </c>
-      <c r="U57" s="9">
+      <c r="U57" s="7">
         <v>26.014862858424252</v>
       </c>
-      <c r="V57" s="9">
+      <c r="V57" s="7">
         <v>25.411902797380879</v>
       </c>
-      <c r="W57" s="9">
+      <c r="W57" s="7">
         <v>25.62920188458909</v>
       </c>
-      <c r="X57" s="9">
+      <c r="X57" s="7">
         <v>25.9831246090082</v>
       </c>
-      <c r="Y57" s="9">
+      <c r="Y57" s="7">
         <v>23.139091158976481</v>
       </c>
-      <c r="Z57" s="9">
+      <c r="Z57" s="7">
         <v>23.069944036531439</v>
       </c>
-      <c r="AA57" s="9">
+      <c r="AA57" s="7">
         <v>22.74176304490166</v>
       </c>
-      <c r="AB57" s="9">
+      <c r="AB57" s="7">
         <v>22.688599758448731</v>
       </c>
-      <c r="AC57" s="9">
+      <c r="AC57" s="7">
         <v>23.251296612530599</v>
       </c>
-      <c r="AD57" s="9">
+      <c r="AD57" s="7">
         <v>23.225903681753081</v>
       </c>
-      <c r="AE57" s="9">
+      <c r="AE57" s="7">
         <v>24.8572021116263</v>
       </c>
-      <c r="AF57" s="9">
+      <c r="AF57" s="7">
         <v>29.319552178114559</v>
       </c>
-      <c r="AG57" s="9">
+      <c r="AG57" s="7">
         <v>44.846971040358653</v>
       </c>
-      <c r="AH57" s="9">
+      <c r="AH57" s="7">
         <v>43.20427568908174</v>
       </c>
-      <c r="AI57" s="9">
+      <c r="AI57" s="7">
         <v>23.280994760951859</v>
       </c>
-      <c r="AJ57" s="9">
+      <c r="AJ57" s="7">
         <v>23.2503943208716</v>
       </c>
-      <c r="AK57" s="9">
+      <c r="AK57" s="7">
         <v>28.893438661207579</v>
       </c>
-      <c r="AL57" s="9">
+      <c r="AL57" s="7">
         <v>23.537602516576779</v>
       </c>
     </row>
     <row r="58" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A58" s="9">
+      <c r="A58" s="7">
         <v>14</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="7">
         <v>30.212737327967069</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="7">
         <v>30.235770992449691</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="7">
         <v>28.79175204370361</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="7">
         <v>29.101978095692179</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58" s="7">
         <v>25.245152368307469</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="7">
         <v>24.964049588754261</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="7">
         <v>26.80249569912883</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="7">
         <v>26.461030287783601</v>
       </c>
-      <c r="J58" s="9">
+      <c r="J58" s="7">
         <v>29.047014560259559</v>
       </c>
-      <c r="K58" s="9">
+      <c r="K58" s="7">
         <v>29.08186574116743</v>
       </c>
-      <c r="L58" s="9">
+      <c r="L58" s="7">
         <v>28.947603428550071</v>
       </c>
-      <c r="M58" s="9">
+      <c r="M58" s="7">
         <v>29.119319017634101</v>
       </c>
-      <c r="N58" s="9">
+      <c r="N58" s="7">
         <v>33.909760611010029</v>
       </c>
-      <c r="O58" s="9">
+      <c r="O58" s="7">
         <v>27.273495651202349</v>
       </c>
-      <c r="P58" s="9">
+      <c r="P58" s="7">
         <v>37.133386419195922</v>
       </c>
-      <c r="Q58" s="9">
+      <c r="Q58" s="7">
         <v>26.32852062631515</v>
       </c>
-      <c r="R58" s="9">
+      <c r="R58" s="7">
         <v>26.241776937044278</v>
       </c>
-      <c r="S58" s="9">
+      <c r="S58" s="7">
         <v>26.324763558046431</v>
       </c>
-      <c r="T58" s="9">
+      <c r="T58" s="7">
         <v>27.26367839335375</v>
       </c>
-      <c r="U58" s="9">
+      <c r="U58" s="7">
         <v>25.733894700551591</v>
       </c>
-      <c r="V58" s="9">
+      <c r="V58" s="7">
         <v>25.415058839680889</v>
       </c>
-      <c r="W58" s="9">
+      <c r="W58" s="7">
         <v>26.049740130965318</v>
       </c>
-      <c r="X58" s="9">
+      <c r="X58" s="7">
         <v>26.32768774165973</v>
       </c>
-      <c r="Y58" s="9">
+      <c r="Y58" s="7">
         <v>23.188865067531669</v>
       </c>
-      <c r="Z58" s="9">
+      <c r="Z58" s="7">
         <v>23.129629839457571</v>
       </c>
-      <c r="AA58" s="9">
+      <c r="AA58" s="7">
         <v>22.793488069424669</v>
       </c>
-      <c r="AB58" s="9">
+      <c r="AB58" s="7">
         <v>22.73846819939082</v>
       </c>
-      <c r="AC58" s="9">
+      <c r="AC58" s="7">
         <v>23.328479284716771</v>
       </c>
-      <c r="AD58" s="9">
+      <c r="AD58" s="7">
         <v>23.303814751252851</v>
       </c>
-      <c r="AE58" s="9">
+      <c r="AE58" s="7">
         <v>24.925700283920861</v>
       </c>
-      <c r="AF58" s="9">
+      <c r="AF58" s="7">
         <v>29.192818501912061</v>
       </c>
-      <c r="AG58" s="9">
+      <c r="AG58" s="7">
         <v>35.179393235186382</v>
       </c>
-      <c r="AH58" s="9">
+      <c r="AH58" s="7">
         <v>34.397696122597523</v>
       </c>
-      <c r="AI58" s="9">
+      <c r="AI58" s="7">
         <v>23.257221141003122</v>
       </c>
-      <c r="AJ58" s="9">
+      <c r="AJ58" s="7">
         <v>23.259797938922361</v>
       </c>
-      <c r="AK58" s="9">
+      <c r="AK58" s="7">
         <v>29.275309365897058</v>
       </c>
-      <c r="AL58" s="9">
+      <c r="AL58" s="7">
         <v>24.878676912826339</v>
       </c>
     </row>
     <row r="59" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A59" s="9">
+      <c r="A59" s="7">
         <v>14.5</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="7">
         <v>30.752876843839381</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="7">
         <v>30.765084503046332</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="7">
         <v>29.124984176268079</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="7">
         <v>29.382528248839829</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="7">
         <v>26.688515330878541</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="7">
         <v>26.4789343669548</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="7">
         <v>27.978532106816768</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="7">
         <v>27.693837257120659</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="7">
         <v>29.360760768917931</v>
       </c>
-      <c r="K59" s="9">
+      <c r="K59" s="7">
         <v>29.379345169618329</v>
       </c>
-      <c r="L59" s="9">
+      <c r="L59" s="7">
         <v>29.128856915504159</v>
       </c>
-      <c r="M59" s="9">
+      <c r="M59" s="7">
         <v>29.255895864824119</v>
       </c>
-      <c r="N59" s="9">
+      <c r="N59" s="7">
         <v>36.539930197025427</v>
       </c>
-      <c r="O59" s="9">
+      <c r="O59" s="7">
         <v>27.50213538821254</v>
       </c>
-      <c r="P59" s="9">
+      <c r="P59" s="7">
         <v>37.375131955124353</v>
       </c>
-      <c r="Q59" s="9">
+      <c r="Q59" s="7">
         <v>26.680413764634</v>
       </c>
-      <c r="R59" s="9">
+      <c r="R59" s="7">
         <v>26.503068739131169</v>
       </c>
-      <c r="S59" s="9">
+      <c r="S59" s="7">
         <v>27.347133891674918</v>
       </c>
-      <c r="T59" s="9">
+      <c r="T59" s="7">
         <v>26.75114069497371</v>
       </c>
-      <c r="U59" s="9">
+      <c r="U59" s="7">
         <v>26.419410055606601</v>
       </c>
-      <c r="V59" s="9">
+      <c r="V59" s="7">
         <v>25.85561644048973</v>
       </c>
-      <c r="W59" s="9">
+      <c r="W59" s="7">
         <v>26.252207373711251</v>
       </c>
-      <c r="X59" s="9">
+      <c r="X59" s="7">
         <v>26.560651366601761</v>
       </c>
-      <c r="Y59" s="9">
+      <c r="Y59" s="7">
         <v>23.297240958493031</v>
       </c>
-      <c r="Z59" s="9">
+      <c r="Z59" s="7">
         <v>23.219884409355949</v>
       </c>
-      <c r="AA59" s="9">
+      <c r="AA59" s="7">
         <v>22.86357337491512</v>
       </c>
-      <c r="AB59" s="9">
+      <c r="AB59" s="7">
         <v>22.80650817759534</v>
       </c>
-      <c r="AC59" s="9">
+      <c r="AC59" s="7">
         <v>23.44760709232213</v>
       </c>
-      <c r="AD59" s="9">
+      <c r="AD59" s="7">
         <v>23.412034147710031</v>
       </c>
-      <c r="AE59" s="9">
+      <c r="AE59" s="7">
         <v>25.02644890625449</v>
       </c>
-      <c r="AF59" s="9">
+      <c r="AF59" s="7">
         <v>28.989286295247918</v>
       </c>
-      <c r="AG59" s="9">
+      <c r="AG59" s="7">
         <v>33.681042851765241</v>
       </c>
-      <c r="AH59" s="9">
+      <c r="AH59" s="7">
         <v>33.033802300080318</v>
       </c>
-      <c r="AI59" s="9">
+      <c r="AI59" s="7">
         <v>23.872729476776101</v>
       </c>
-      <c r="AJ59" s="9">
+      <c r="AJ59" s="7">
         <v>23.878215565160129</v>
       </c>
-      <c r="AK59" s="9">
+      <c r="AK59" s="7">
         <v>30.218662064811351</v>
       </c>
-      <c r="AL59" s="9">
+      <c r="AL59" s="7">
         <v>26.173344609289519</v>
       </c>
     </row>
     <row r="60" spans="1:38" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A60" s="9">
+      <c r="A60" s="7">
         <v>15</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="7">
         <v>29.75108958847845</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="7">
         <v>29.927932727975499</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="7">
         <v>29.28683706580065</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="7">
         <v>29.50472311141607</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="7">
         <v>26.534723087923421</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="7">
         <v>26.54891596956265</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="7">
         <v>24.567967580475258</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="7">
         <v>24.931700237052841</v>
       </c>
-      <c r="J60" s="9">
+      <c r="J60" s="7">
         <v>29.181760009482421</v>
       </c>
-      <c r="K60" s="9">
+      <c r="K60" s="7">
         <v>29.21000346339353</v>
       </c>
-      <c r="L60" s="9">
+      <c r="L60" s="7">
         <v>29.613441366657579</v>
       </c>
-      <c r="M60" s="9">
+      <c r="M60" s="7">
         <v>29.647079042382149</v>
       </c>
-      <c r="N60" s="9">
+      <c r="N60" s="7">
         <v>33.856558929612618</v>
       </c>
-      <c r="O60" s="9">
+      <c r="O60" s="7">
         <v>27.559616686616891</v>
       </c>
-      <c r="P60" s="9">
+      <c r="P60" s="7">
         <v>36.637799955785518</v>
       </c>
-      <c r="Q60" s="9">
+      <c r="Q60" s="7">
         <v>26.353538705955032</v>
       </c>
-      <c r="R60" s="9">
+      <c r="R60" s="7">
         <v>26.328026665444121</v>
       </c>
-      <c r="S60" s="9">
+      <c r="S60" s="7">
         <v>27.005651260571799</v>
       </c>
-      <c r="T60" s="9">
+      <c r="T60" s="7">
         <v>26.78799068967475</v>
       </c>
-      <c r="U60" s="9">
+      <c r="U60" s="7">
         <v>26.713738679663059</v>
       </c>
-      <c r="V60" s="9">
+      <c r="V60" s="7">
         <v>26.004464970133</v>
       </c>
-      <c r="W60" s="9">
+      <c r="W60" s="7">
         <v>26.172314349263001</v>
       </c>
-      <c r="X60" s="9">
+      <c r="X60" s="7">
         <v>26.581515684322351</v>
       </c>
-      <c r="Y60" s="9">
+      <c r="Y60" s="7">
         <v>23.365351632063721</v>
       </c>
-      <c r="Z60" s="9">
+      <c r="Z60" s="7">
         <v>23.270050581649151</v>
       </c>
-      <c r="AA60" s="9">
+      <c r="AA60" s="7">
         <v>22.893253128983659</v>
       </c>
-      <c r="AB60" s="9">
+      <c r="AB60" s="7">
         <v>22.835346042744199</v>
       </c>
-      <c r="AC60" s="9">
+      <c r="AC60" s="7">
         <v>23.523070736631471</v>
       </c>
-      <c r="AD60" s="9">
+      <c r="AD60" s="7">
         <v>23.47667702418298</v>
       </c>
-      <c r="AE60" s="9">
+      <c r="AE60" s="7">
         <v>24.92657331793421</v>
       </c>
-      <c r="AF60" s="9">
+      <c r="AF60" s="7">
         <v>28.270592310993401</v>
       </c>
-      <c r="AG60" s="9">
+      <c r="AG60" s="7">
         <v>30.89918813681588</v>
       </c>
-      <c r="AH60" s="9">
+      <c r="AH60" s="7">
         <v>30.47560122591597</v>
       </c>
-      <c r="AI60" s="9">
+      <c r="AI60" s="7">
         <v>23.724002954550791</v>
       </c>
-      <c r="AJ60" s="9">
+      <c r="AJ60" s="7">
         <v>23.706179758993539</v>
       </c>
-      <c r="AK60" s="9">
+      <c r="AK60" s="7">
         <v>29.943092047755879</v>
       </c>
-      <c r="AL60" s="9">
+      <c r="AL60" s="7">
         <v>26.760924264946571</v>
       </c>
     </row>
